--- a/AAII_Financials/Quarterly/TGEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TGEN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/TGEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TGEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>TGEN</t>
   </si>
@@ -656,416 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F8" s="3">
         <v>7100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>6700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>5400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>4500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>6600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>6400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>7400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>7200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>5000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>6100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>6100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>5700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>7200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>7400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>8000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>8700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>8700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>7900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>8200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>9300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>7900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>8500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>10200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>10300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>8500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>7600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>6800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>7100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F9" s="3">
         <v>4200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3700</v>
-      </c>
-      <c r="I9" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J9" s="3">
-        <v>4300</v>
       </c>
       <c r="K9" s="3">
         <v>3700</v>
       </c>
       <c r="L9" s="3">
+        <v>4300</v>
+      </c>
+      <c r="M9" s="3">
+        <v>3700</v>
+      </c>
+      <c r="N9" s="3">
         <v>2700</v>
-      </c>
-      <c r="M9" s="3">
-        <v>3300</v>
-      </c>
-      <c r="N9" s="3">
-        <v>3100</v>
       </c>
       <c r="O9" s="3">
         <v>3300</v>
       </c>
       <c r="P9" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>3300</v>
+      </c>
+      <c r="R9" s="3">
         <v>4400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>4500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>5200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>5400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>5800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>4400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>5200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>5600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>5100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>5300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>6300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>6500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>5200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>4600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>3900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>4400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F10" s="3">
         <v>2900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>2800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>2300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>2700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>3100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>3500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>2800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>3000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>2400</v>
-      </c>
-      <c r="P10" s="3">
-        <v>2800</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>2900</v>
       </c>
       <c r="R10" s="3">
         <v>2800</v>
       </c>
       <c r="S10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="T10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="U10" s="3">
         <v>3300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>3500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>3000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>3700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>2800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>3200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>3900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>3800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>3300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>3000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>2900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>2700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,13 +1123,15 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E12" s="3">
         <v>200</v>
@@ -1122,7 +1149,7 @@
         <v>200</v>
       </c>
       <c r="J12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K12" s="3">
         <v>200</v>
@@ -1131,7 +1158,7 @@
         <v>100</v>
       </c>
       <c r="M12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N12" s="3">
         <v>100</v>
@@ -1143,13 +1170,13 @@
         <v>100</v>
       </c>
       <c r="Q12" s="3">
+        <v>100</v>
+      </c>
+      <c r="R12" s="3">
+        <v>100</v>
+      </c>
+      <c r="S12" s="3">
         <v>200</v>
-      </c>
-      <c r="R12" s="3">
-        <v>400</v>
-      </c>
-      <c r="S12" s="3">
-        <v>400</v>
       </c>
       <c r="T12" s="3">
         <v>400</v>
@@ -1158,40 +1185,46 @@
         <v>400</v>
       </c>
       <c r="V12" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="W12" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="X12" s="3">
         <v>300</v>
       </c>
       <c r="Y12" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Z12" s="3">
         <v>300</v>
       </c>
       <c r="AA12" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB12" s="3">
         <v>300</v>
       </c>
-      <c r="AB12" s="3">
-        <v>200</v>
-      </c>
       <c r="AC12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AD12" s="3">
         <v>200</v>
       </c>
       <c r="AE12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AF12" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH12" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,25 +1315,31 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>19</v>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1312,46 +1351,46 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-2400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-1900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>2900</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>3700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>4400</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>19</v>
@@ -1365,17 +1404,23 @@
       <c r="AC14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F17" s="3">
         <v>7500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>7500</v>
-      </c>
-      <c r="F17" s="3">
-        <v>6800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>5900</v>
       </c>
       <c r="H17" s="3">
         <v>6800</v>
       </c>
       <c r="I17" s="3">
+        <v>5900</v>
+      </c>
+      <c r="J17" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K17" s="3">
         <v>7200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>7400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>7000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>5700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>9800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>7400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>7900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>9100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>9200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>9200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>8200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>11500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>13700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>8500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>9100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>10100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>10000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>8400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>7800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>6800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>7100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-800</v>
       </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
         <v>200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-4100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-500</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-1100</v>
       </c>
       <c r="S18" s="3">
         <v>-500</v>
       </c>
       <c r="T18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="U18" s="3">
         <v>-500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W18" s="3">
         <v>-300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-3300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-4400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>300</v>
       </c>
       <c r="AB18" s="3">
         <v>100</v>
       </c>
       <c r="AC18" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-200</v>
       </c>
-      <c r="AD18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>0</v>
-      </c>
       <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1715,23 +1780,25 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1739,29 +1806,29 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1775,23 +1842,23 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
@@ -1807,100 +1874,112 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-4000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-1000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-3200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-4300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1944,17 +2023,17 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
@@ -1962,14 +2041,14 @@
         <v>0</v>
       </c>
       <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
@@ -1991,100 +2070,112 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-4200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-3400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-4500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-700</v>
       </c>
-      <c r="Z23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="3">
         <v>300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-300</v>
       </c>
-      <c r="AD23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>0</v>
-      </c>
       <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -2154,8 +2245,8 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>19</v>
+      <c r="Z24" s="3">
+        <v>0</v>
       </c>
       <c r="AA24" s="3">
         <v>0</v>
@@ -2163,8 +2254,8 @@
       <c r="AB24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>19</v>
+      <c r="AC24" s="3">
+        <v>0</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>19</v>
@@ -2175,8 +2266,14 @@
       <c r="AF24" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH24" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>1800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-4200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-3400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-4500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-700</v>
       </c>
-      <c r="Z26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="3">
         <v>300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-300</v>
       </c>
-      <c r="AD26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>0</v>
-      </c>
       <c r="AF26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-4100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-3300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-4400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-800</v>
       </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="3">
         <v>300</v>
       </c>
-      <c r="AB27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-300</v>
       </c>
-      <c r="AD27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>0</v>
-      </c>
       <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,23 +2952,29 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -2843,29 +2982,29 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2879,23 +3018,23 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
@@ -2911,100 +3050,112 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>1800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-4100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-3300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-4400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-800</v>
       </c>
-      <c r="Z33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="3">
         <v>300</v>
       </c>
-      <c r="AB33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-300</v>
       </c>
-      <c r="AD33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>0</v>
-      </c>
       <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>1800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-4100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-3300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-4400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-800</v>
       </c>
-      <c r="Z35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="3">
         <v>300</v>
       </c>
-      <c r="AB35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-300</v>
       </c>
-      <c r="AD35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>0</v>
-      </c>
       <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3523,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F41" s="3">
         <v>600</v>
-      </c>
-      <c r="E41" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F41" s="3">
-        <v>1600</v>
       </c>
       <c r="G41" s="3">
         <v>1900</v>
       </c>
       <c r="H41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J41" s="3">
         <v>2900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>5500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>3700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1700</v>
-      </c>
-      <c r="AB41" s="3">
-        <v>2100</v>
-      </c>
-      <c r="AC41" s="3">
-        <v>3300</v>
       </c>
       <c r="AD41" s="3">
         <v>2100</v>
       </c>
       <c r="AE41" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AF41" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AG41" s="3">
         <v>3700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,192 +3715,210 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F43" s="3">
         <v>9500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>7400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>8600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>9200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>11300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>11700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>11800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>13000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>12800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>12400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>12200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>12900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>14300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>13000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>17100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>20000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>18100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>17500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>16900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>19100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>16000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>16000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>16500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>14100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>14700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>12500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>11800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>11200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F44" s="3">
         <v>11000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>12000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>11900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>10500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>8700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>8200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>7800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>7800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>7900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>6800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>6800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>7200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>7100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>7300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>7500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>6400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>7100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>7000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>6700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>6300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>6000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>5500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>5100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>5100</v>
-      </c>
-      <c r="AB44" s="3">
-        <v>6100</v>
-      </c>
-      <c r="AC44" s="3">
-        <v>6100</v>
       </c>
       <c r="AD44" s="3">
         <v>6100</v>
       </c>
       <c r="AE44" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AF44" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AG44" s="3">
         <v>4800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3729,22 +3926,22 @@
         <v>400</v>
       </c>
       <c r="E45" s="3">
+        <v>400</v>
+      </c>
+      <c r="F45" s="3">
+        <v>400</v>
+      </c>
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>600</v>
-      </c>
-      <c r="J45" s="3">
-        <v>600</v>
       </c>
       <c r="K45" s="3">
         <v>600</v>
@@ -3753,22 +3950,22 @@
         <v>600</v>
       </c>
       <c r="M45" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="N45" s="3">
         <v>600</v>
       </c>
       <c r="O45" s="3">
+        <v>800</v>
+      </c>
+      <c r="P45" s="3">
         <v>600</v>
-      </c>
-      <c r="P45" s="3">
-        <v>500</v>
       </c>
       <c r="Q45" s="3">
         <v>600</v>
       </c>
       <c r="R45" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="S45" s="3">
         <v>600</v>
@@ -3783,134 +3980,146 @@
         <v>600</v>
       </c>
       <c r="W45" s="3">
+        <v>600</v>
+      </c>
+      <c r="X45" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y45" s="3">
         <v>700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>900</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>800</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>700</v>
       </c>
       <c r="AC45" s="3">
         <v>800</v>
       </c>
       <c r="AD45" s="3">
+        <v>700</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF45" s="3">
         <v>600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>20300</v>
+      </c>
+      <c r="F46" s="3">
         <v>21600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>21800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>22400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>22000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>23400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>23400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>25600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>25000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>24700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>23200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>23300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>22200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>23600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>23800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>26100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>27900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>26600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>26200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>26800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>26400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>22900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>23400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>23700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>21700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>23600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>22700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>20600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>20100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>100</v>
+      <c r="D47" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E47" s="3">
         <v>100</v>
@@ -3927,11 +4136,11 @@
       <c r="I47" s="3">
         <v>100</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>19</v>
+      <c r="J47" s="3">
+        <v>100</v>
+      </c>
+      <c r="K47" s="3">
+        <v>100</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>19</v>
@@ -3945,11 +4154,11 @@
       <c r="O47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3987,177 +4196,189 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-      <c r="AD47" s="3" t="s">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AE47" s="3" t="s">
+      <c r="AG47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F48" s="3">
         <v>2000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>4800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>5100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>5400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>5600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>5900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>6200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>6500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>11300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>11100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>11400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>12000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>12300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>15500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>15700</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>500</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>500</v>
       </c>
       <c r="AF48" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH48" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F49" s="3">
         <v>5400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>5600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>3400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>3400</v>
-      </c>
-      <c r="H49" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I49" s="3">
-        <v>3500</v>
       </c>
       <c r="J49" s="3">
         <v>3500</v>
       </c>
       <c r="K49" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L49" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M49" s="3">
         <v>3600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>3600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>3700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>3800</v>
-      </c>
-      <c r="P49" s="3">
-        <v>6700</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>6800</v>
       </c>
       <c r="R49" s="3">
         <v>6700</v>
       </c>
       <c r="S49" s="3">
+        <v>6800</v>
+      </c>
+      <c r="T49" s="3">
+        <v>6700</v>
+      </c>
+      <c r="U49" s="3">
         <v>6900</v>
-      </c>
-      <c r="T49" s="3">
-        <v>6900</v>
-      </c>
-      <c r="U49" s="3">
-        <v>6800</v>
       </c>
       <c r="V49" s="3">
         <v>6900</v>
       </c>
       <c r="W49" s="3">
+        <v>6800</v>
+      </c>
+      <c r="X49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Y49" s="3">
         <v>11900</v>
-      </c>
-      <c r="X49" s="3">
-        <v>16300</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>16300</v>
       </c>
       <c r="Z49" s="3">
         <v>16300</v>
@@ -4166,22 +4387,28 @@
         <v>16300</v>
       </c>
       <c r="AB49" s="3">
+        <v>16300</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>16300</v>
+      </c>
+      <c r="AD49" s="3">
         <v>2500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>2100</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>1100</v>
       </c>
       <c r="AF49" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,13 +4597,19 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E52" s="3">
         <v>100</v>
@@ -4388,7 +4627,7 @@
         <v>100</v>
       </c>
       <c r="J52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
@@ -4397,7 +4636,7 @@
         <v>200</v>
       </c>
       <c r="M52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N52" s="3">
         <v>200</v>
@@ -4412,52 +4651,58 @@
         <v>200</v>
       </c>
       <c r="R52" s="3">
+        <v>200</v>
+      </c>
+      <c r="S52" s="3">
+        <v>200</v>
+      </c>
+      <c r="T52" s="3">
         <v>300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>300</v>
-      </c>
-      <c r="W52" s="3">
-        <v>400</v>
-      </c>
-      <c r="X52" s="3">
-        <v>400</v>
       </c>
       <c r="Y52" s="3">
         <v>400</v>
       </c>
       <c r="Z52" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB52" s="3">
         <v>500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>15100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>15000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>2100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>2100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>27800</v>
+      </c>
+      <c r="F54" s="3">
         <v>29200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>29800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>28200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>28300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>30100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>30300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>32800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>32400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>32500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>31300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>31600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>30100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>35200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>35900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>38500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>41100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>40000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>39800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>40400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>49900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>50800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>51500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>52500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>50700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>56600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>55600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>24400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>23700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>23200</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,123 +4967,131 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
+        <v>4500</v>
+      </c>
+      <c r="G57" s="3">
         <v>4200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>4200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>3300</v>
-      </c>
-      <c r="H57" s="3">
-        <v>3300</v>
       </c>
       <c r="I57" s="3">
         <v>3300</v>
       </c>
       <c r="J57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L57" s="3">
         <v>4400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>3400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>4200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>3800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>4100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>5500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>5300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>6500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>6200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>5900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>7200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>5700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>5000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>6800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>5100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>5400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>4500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>4000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>3400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4839,43 +5106,43 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>2400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>900</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>2000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>2600</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>900</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>900</v>
       </c>
       <c r="AB58" s="3">
         <v>900</v>
@@ -4883,209 +5150,227 @@
       <c r="AC58" s="3">
         <v>900</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE58" s="3" t="s">
-        <v>19</v>
+      <c r="AD58" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE58" s="3">
+        <v>900</v>
       </c>
       <c r="AF58" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH58" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F59" s="3">
         <v>5600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>6000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>5200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>4400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>4500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>4500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>4900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>4700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>4500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>4500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>5200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>5800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>4100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>4400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>4700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>4000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>3900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>3800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>3300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>2800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>3200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>3100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>2100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>2300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F60" s="3">
         <v>10100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>10200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>9400</v>
-      </c>
-      <c r="G60" s="3">
-        <v>7700</v>
-      </c>
-      <c r="H60" s="3">
-        <v>7800</v>
       </c>
       <c r="I60" s="3">
         <v>7700</v>
       </c>
       <c r="J60" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K60" s="3">
+        <v>7700</v>
+      </c>
+      <c r="L60" s="3">
         <v>9300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>8800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>8200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7200</v>
-      </c>
-      <c r="O60" s="3">
-        <v>8800</v>
-      </c>
-      <c r="P60" s="3">
-        <v>8500</v>
       </c>
       <c r="Q60" s="3">
         <v>8800</v>
       </c>
       <c r="R60" s="3">
+        <v>8500</v>
+      </c>
+      <c r="S60" s="3">
+        <v>8800</v>
+      </c>
+      <c r="T60" s="3">
         <v>12200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>13400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>11600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>10600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>10600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>13200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>11300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>11300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>11000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>8700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>9400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>8500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>6100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>5600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -5109,26 +5394,26 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>1900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1700</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -5154,10 +5439,10 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
-        <v>3100</v>
+        <v>0</v>
       </c>
       <c r="AC61" s="3">
-        <v>3100</v>
+        <v>0</v>
       </c>
       <c r="AD61" s="3">
         <v>3100</v>
@@ -5168,100 +5453,112 @@
       <c r="AF61" s="3">
         <v>3100</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F62" s="3">
         <v>2700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>2500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>3200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>3500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>3500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>4300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>4600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>4800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>5200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>8700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>6900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>7100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>7800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>8300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>10700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>10800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>13000</v>
+      </c>
+      <c r="F66" s="3">
         <v>12700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>12900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>10600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>9200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>9600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>9700</v>
-      </c>
-      <c r="J66" s="3">
-        <v>11400</v>
-      </c>
-      <c r="K66" s="3">
-        <v>11200</v>
       </c>
       <c r="L66" s="3">
         <v>11400</v>
       </c>
       <c r="M66" s="3">
+        <v>11200</v>
+      </c>
+      <c r="N66" s="3">
+        <v>11400</v>
+      </c>
+      <c r="O66" s="3">
         <v>11700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>12500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>12800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>13900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>14400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>16300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>17800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>16200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>15500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>15900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>22100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>18700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>18800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>19200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>17400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>23800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>22900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>9700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>9200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-42900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-41000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-40600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-39800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-38300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-36900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-36600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-35700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-35800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-35900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-37400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-37800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-39500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-35500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-35200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-34600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-33400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-32900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-32300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-32000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-28700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-24300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-23700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-22900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-22800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-23100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-23100</v>
-      </c>
-      <c r="AD72" s="3">
-        <v>-22800</v>
-      </c>
-      <c r="AE72" s="3">
-        <v>-22800</v>
       </c>
       <c r="AF72" s="3">
         <v>-22800</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="AH72" s="3">
+        <v>-22800</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>14700</v>
+      </c>
+      <c r="F76" s="3">
         <v>16500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>16900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>17700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>19100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>20400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>20600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>21400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>21200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>21100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>19600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>19100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>17300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>21300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>21500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>22100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>23300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>23700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>24200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>24600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>27800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>32100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>32600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>33300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>33200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>32900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>32700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>14700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>14500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>1800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-4100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-3300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-4400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-800</v>
       </c>
-      <c r="Z81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="3">
         <v>300</v>
       </c>
-      <c r="AB81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-300</v>
       </c>
-      <c r="AD81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>0</v>
-      </c>
       <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,22 +7200,24 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>200</v>
-      </c>
-      <c r="F83" s="3">
-        <v>100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -6865,10 +7262,10 @@
         <v>100</v>
       </c>
       <c r="V83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X83" s="3">
         <v>200</v>
@@ -6889,16 +7286,22 @@
         <v>200</v>
       </c>
       <c r="AD83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AE83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AF83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-2500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1100</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-600</v>
       </c>
       <c r="W89" s="3">
         <v>-1500</v>
       </c>
       <c r="X89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="Z89" s="3">
         <v>200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,13 +7922,15 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -7501,16 +7942,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
@@ -7519,7 +7960,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -7531,14 +7972,14 @@
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
@@ -7546,25 +7987,25 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-600</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
       </c>
       <c r="Z91" s="3">
         <v>-100</v>
       </c>
       <c r="AA91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="AB91" s="3">
         <v>-100</v>
       </c>
       <c r="AC91" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="AD91" s="3">
         <v>-100</v>
@@ -7573,10 +8014,16 @@
         <v>-100</v>
       </c>
       <c r="AF91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +8212,14 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7768,40 +8227,40 @@
         <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
       <c r="P94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -7810,49 +8269,55 @@
         <v>-100</v>
       </c>
       <c r="S94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T94" s="3">
         <v>-100</v>
       </c>
       <c r="U94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>5000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>1400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>1300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8738,14 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8262,7 +8753,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
@@ -8289,64 +8780,70 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>1900</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>1500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>900</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>-2000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>1700</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8934,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1000</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-2600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>2200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>1900</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-1500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>2300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>1200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TGEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TGEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>TGEN</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E8" s="3">
         <v>6200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5000</v>
-      </c>
-      <c r="O8" s="3">
-        <v>6100</v>
       </c>
       <c r="P8" s="3">
         <v>6100</v>
       </c>
       <c r="Q8" s="3">
+        <v>6100</v>
+      </c>
+      <c r="R8" s="3">
         <v>5700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8000</v>
-      </c>
-      <c r="U8" s="3">
-        <v>8700</v>
       </c>
       <c r="V8" s="3">
         <v>8700</v>
       </c>
       <c r="W8" s="3">
+        <v>8700</v>
+      </c>
+      <c r="X8" s="3">
         <v>7900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>10200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E9" s="3">
         <v>3600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>3700</v>
       </c>
       <c r="K9" s="3">
         <v>3700</v>
       </c>
       <c r="L9" s="3">
+        <v>3700</v>
+      </c>
+      <c r="M9" s="3">
         <v>4300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>6500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E10" s="3">
         <v>2600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,16 +1138,17 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>200</v>
+      </c>
+      <c r="E12" s="3">
         <v>300</v>
-      </c>
-      <c r="E12" s="3">
-        <v>200</v>
       </c>
       <c r="F12" s="3">
         <v>200</v>
@@ -1155,13 +1169,13 @@
         <v>200</v>
       </c>
       <c r="L12" s="3">
+        <v>200</v>
+      </c>
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>200</v>
-      </c>
-      <c r="N12" s="3">
-        <v>100</v>
       </c>
       <c r="O12" s="3">
         <v>100</v>
@@ -1176,10 +1190,10 @@
         <v>100</v>
       </c>
       <c r="S12" s="3">
+        <v>100</v>
+      </c>
+      <c r="T12" s="3">
         <v>200</v>
-      </c>
-      <c r="T12" s="3">
-        <v>400</v>
       </c>
       <c r="U12" s="3">
         <v>400</v>
@@ -1191,7 +1205,7 @@
         <v>400</v>
       </c>
       <c r="X12" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Y12" s="3">
         <v>300</v>
@@ -1200,16 +1214,16 @@
         <v>300</v>
       </c>
       <c r="AA12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB12" s="3">
         <v>400</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>300</v>
       </c>
       <c r="AC12" s="3">
         <v>300</v>
       </c>
       <c r="AD12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AE12" s="3">
         <v>200</v>
@@ -1218,13 +1232,16 @@
         <v>200</v>
       </c>
       <c r="AG12" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH12" s="3">
         <v>100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,19 +1338,22 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>19</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>19</v>
@@ -1341,8 +1361,8 @@
       <c r="H14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1357,43 +1377,43 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-2400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2900</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>19</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y14" s="3">
         <v>3700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>4400</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>19</v>
@@ -1410,8 +1430,8 @@
       <c r="AE14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E17" s="3">
         <v>7200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7700</v>
-      </c>
-      <c r="F17" s="3">
-        <v>7500</v>
       </c>
       <c r="G17" s="3">
         <v>7500</v>
       </c>
       <c r="H17" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I17" s="3">
         <v>6800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9100</v>
-      </c>
-      <c r="U17" s="3">
-        <v>9200</v>
       </c>
       <c r="V17" s="3">
         <v>9200</v>
       </c>
       <c r="W17" s="3">
+        <v>9200</v>
+      </c>
+      <c r="X17" s="3">
         <v>8200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>11500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>10100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-1400</v>
       </c>
       <c r="I18" s="3">
         <v>-1400</v>
       </c>
       <c r="J18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K18" s="3">
         <v>-200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-800</v>
       </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
       <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
         <v>200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1100</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-500</v>
       </c>
       <c r="V18" s="3">
         <v>-500</v>
       </c>
       <c r="W18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X18" s="3">
         <v>-300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-600</v>
       </c>
       <c r="AA18" s="3">
         <v>-600</v>
       </c>
       <c r="AB18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AC18" s="3">
         <v>100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-200</v>
       </c>
-      <c r="AF18" s="3">
-        <v>0</v>
-      </c>
       <c r="AG18" s="3">
         <v>0</v>
       </c>
       <c r="AH18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1794,14 +1828,14 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1812,26 +1846,26 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1848,20 +1882,20 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -1880,106 +1914,112 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-600</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-1300</v>
       </c>
       <c r="I21" s="3">
         <v>-1300</v>
       </c>
       <c r="J21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K21" s="3">
         <v>-100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-700</v>
-      </c>
-      <c r="L21" s="3">
-        <v>200</v>
       </c>
       <c r="M21" s="3">
         <v>200</v>
       </c>
       <c r="N21" s="3">
+        <v>200</v>
+      </c>
+      <c r="O21" s="3">
         <v>1600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1000</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-400</v>
       </c>
       <c r="V21" s="3">
         <v>-400</v>
       </c>
       <c r="W21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="X21" s="3">
         <v>-200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-100</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>100</v>
       </c>
       <c r="AG21" s="3">
         <v>100</v>
       </c>
       <c r="AH21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2029,13 +2069,13 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T22" s="3">
         <v>100</v>
       </c>
       <c r="U22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -2047,11 +2087,11 @@
         <v>0</v>
       </c>
       <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
         <v>100</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
@@ -2076,106 +2116,112 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-800</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-1400</v>
       </c>
       <c r="I23" s="3">
         <v>-1400</v>
       </c>
       <c r="J23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K23" s="3">
         <v>-200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-800</v>
-      </c>
-      <c r="L23" s="3">
-        <v>100</v>
       </c>
       <c r="M23" s="3">
         <v>100</v>
       </c>
       <c r="N23" s="3">
+        <v>100</v>
+      </c>
+      <c r="O23" s="3">
         <v>1500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-700</v>
       </c>
-      <c r="AB23" s="3">
-        <v>0</v>
-      </c>
       <c r="AC23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="3">
         <v>300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-300</v>
       </c>
-      <c r="AF23" s="3">
-        <v>0</v>
-      </c>
       <c r="AG23" s="3">
         <v>0</v>
       </c>
       <c r="AH23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -2251,14 +2297,14 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-      <c r="AB24" s="3" t="s">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="3" t="s">
-        <v>19</v>
+      <c r="AD24" s="3">
+        <v>0</v>
       </c>
       <c r="AE24" s="3" t="s">
         <v>19</v>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-800</v>
-      </c>
-      <c r="L26" s="3">
-        <v>100</v>
       </c>
       <c r="M26" s="3">
         <v>100</v>
       </c>
       <c r="N26" s="3">
+        <v>100</v>
+      </c>
+      <c r="O26" s="3">
         <v>1500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-700</v>
       </c>
-      <c r="AB26" s="3">
-        <v>0</v>
-      </c>
       <c r="AC26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="3">
         <v>300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-300</v>
       </c>
-      <c r="AF26" s="3">
-        <v>0</v>
-      </c>
       <c r="AG26" s="3">
         <v>0</v>
       </c>
       <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-900</v>
-      </c>
-      <c r="L27" s="3">
-        <v>100</v>
       </c>
       <c r="M27" s="3">
         <v>100</v>
       </c>
       <c r="N27" s="3">
+        <v>100</v>
+      </c>
+      <c r="O27" s="3">
         <v>1500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-800</v>
       </c>
-      <c r="AB27" s="3">
-        <v>0</v>
-      </c>
       <c r="AC27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="3">
         <v>300</v>
       </c>
-      <c r="AD27" s="3">
-        <v>0</v>
-      </c>
       <c r="AE27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-300</v>
       </c>
-      <c r="AF27" s="3">
-        <v>0</v>
-      </c>
       <c r="AG27" s="3">
         <v>0</v>
       </c>
       <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2970,14 +3040,14 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -2988,26 +3058,26 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -3024,20 +3094,20 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -3056,106 +3126,112 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-900</v>
-      </c>
-      <c r="L33" s="3">
-        <v>100</v>
       </c>
       <c r="M33" s="3">
         <v>100</v>
       </c>
       <c r="N33" s="3">
+        <v>100</v>
+      </c>
+      <c r="O33" s="3">
         <v>1500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-800</v>
       </c>
-      <c r="AB33" s="3">
-        <v>0</v>
-      </c>
       <c r="AC33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="3">
         <v>300</v>
       </c>
-      <c r="AD33" s="3">
-        <v>0</v>
-      </c>
       <c r="AE33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-300</v>
       </c>
-      <c r="AF33" s="3">
-        <v>0</v>
-      </c>
       <c r="AG33" s="3">
         <v>0</v>
       </c>
       <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-900</v>
-      </c>
-      <c r="L35" s="3">
-        <v>100</v>
       </c>
       <c r="M35" s="3">
         <v>100</v>
       </c>
       <c r="N35" s="3">
+        <v>100</v>
+      </c>
+      <c r="O35" s="3">
         <v>1500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-800</v>
       </c>
-      <c r="AB35" s="3">
-        <v>0</v>
-      </c>
       <c r="AC35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="3">
         <v>300</v>
       </c>
-      <c r="AD35" s="3">
-        <v>0</v>
-      </c>
       <c r="AE35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-300</v>
       </c>
-      <c r="AF35" s="3">
-        <v>0</v>
-      </c>
       <c r="AG35" s="3">
         <v>0</v>
       </c>
       <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2900</v>
-      </c>
-      <c r="T41" s="3">
-        <v>900</v>
       </c>
       <c r="U41" s="3">
         <v>900</v>
       </c>
       <c r="V41" s="3">
+        <v>900</v>
+      </c>
+      <c r="W41" s="3">
         <v>800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,189 +3811,195 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E43" s="3">
         <v>7800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>14300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>17100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>20000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>18100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>17500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>16900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>19100</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>16000</v>
       </c>
       <c r="AA43" s="3">
         <v>16000</v>
       </c>
       <c r="AB43" s="3">
+        <v>16000</v>
+      </c>
+      <c r="AC43" s="3">
         <v>16500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>14100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>14700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>12500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>11800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>11200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E44" s="3">
         <v>10000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>11000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>12000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>11900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>10500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>8700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8200</v>
-      </c>
-      <c r="L44" s="3">
-        <v>7800</v>
       </c>
       <c r="M44" s="3">
         <v>7800</v>
       </c>
       <c r="N44" s="3">
+        <v>7800</v>
+      </c>
+      <c r="O44" s="3">
         <v>7900</v>
-      </c>
-      <c r="O44" s="3">
-        <v>6800</v>
       </c>
       <c r="P44" s="3">
         <v>6800</v>
       </c>
       <c r="Q44" s="3">
+        <v>6800</v>
+      </c>
+      <c r="R44" s="3">
         <v>7200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>7500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>6400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>7000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>6300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>6000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5500</v>
-      </c>
-      <c r="AB44" s="3">
-        <v>5100</v>
       </c>
       <c r="AC44" s="3">
         <v>5100</v>
       </c>
       <c r="AD44" s="3">
-        <v>6100</v>
+        <v>5100</v>
       </c>
       <c r="AE44" s="3">
         <v>6100</v>
@@ -3912,18 +4008,21 @@
         <v>6100</v>
       </c>
       <c r="AG44" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AH44" s="3">
         <v>4800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E45" s="3">
         <v>400</v>
@@ -3932,19 +4031,19 @@
         <v>400</v>
       </c>
       <c r="G45" s="3">
+        <v>400</v>
+      </c>
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>600</v>
       </c>
       <c r="L45" s="3">
         <v>600</v>
@@ -3956,19 +4055,19 @@
         <v>600</v>
       </c>
       <c r="O45" s="3">
+        <v>600</v>
+      </c>
+      <c r="P45" s="3">
         <v>800</v>
-      </c>
-      <c r="P45" s="3">
-        <v>600</v>
       </c>
       <c r="Q45" s="3">
         <v>600</v>
       </c>
       <c r="R45" s="3">
+        <v>600</v>
+      </c>
+      <c r="S45" s="3">
         <v>500</v>
-      </c>
-      <c r="S45" s="3">
-        <v>600</v>
       </c>
       <c r="T45" s="3">
         <v>600</v>
@@ -3986,143 +4085,149 @@
         <v>600</v>
       </c>
       <c r="Y45" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z45" s="3">
         <v>700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>800</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>900</v>
       </c>
       <c r="AB45" s="3">
         <v>900</v>
       </c>
       <c r="AC45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD45" s="3">
         <v>800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E46" s="3">
         <v>19700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22000</v>
-      </c>
-      <c r="J46" s="3">
-        <v>23400</v>
       </c>
       <c r="K46" s="3">
         <v>23400</v>
       </c>
       <c r="L46" s="3">
+        <v>23400</v>
+      </c>
+      <c r="M46" s="3">
         <v>25600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>25000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>24700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>23200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>23300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>22200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>23600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>23800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>26100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>27900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>26600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>26200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>26800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>26400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>22900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>23400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>23700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>21700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>23600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>22700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>20600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>20100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="3">
+        <v>100</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="E47" s="3">
-        <v>100</v>
       </c>
       <c r="F47" s="3">
         <v>100</v>
@@ -4142,8 +4247,8 @@
       <c r="K47" s="3">
         <v>100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>19</v>
+      <c r="L47" s="3">
+        <v>100</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>19</v>
@@ -4160,8 +4265,8 @@
       <c r="Q47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -4202,106 +4307,109 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>19</v>
+      <c r="AF47" s="3">
+        <v>0</v>
       </c>
       <c r="AG47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AH47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI47" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E48" s="3">
         <v>3300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>15500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>15700</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>500</v>
       </c>
       <c r="AG48" s="3">
         <v>500</v>
@@ -4309,31 +4417,34 @@
       <c r="AH48" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="E49" s="3">
         <v>5200</v>
       </c>
       <c r="F49" s="3">
+        <v>5200</v>
+      </c>
+      <c r="G49" s="3">
         <v>5400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5600</v>
-      </c>
-      <c r="H49" s="3">
-        <v>3400</v>
       </c>
       <c r="I49" s="3">
         <v>3400</v>
       </c>
       <c r="J49" s="3">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="K49" s="3">
         <v>3500</v>
@@ -4342,46 +4453,46 @@
         <v>3500</v>
       </c>
       <c r="M49" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="N49" s="3">
         <v>3600</v>
       </c>
       <c r="O49" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="P49" s="3">
         <v>3700</v>
       </c>
       <c r="Q49" s="3">
+        <v>3700</v>
+      </c>
+      <c r="R49" s="3">
         <v>3800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6700</v>
-      </c>
-      <c r="U49" s="3">
-        <v>6900</v>
       </c>
       <c r="V49" s="3">
         <v>6900</v>
       </c>
       <c r="W49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="X49" s="3">
         <v>6800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>11900</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>16300</v>
       </c>
       <c r="AA49" s="3">
         <v>16300</v>
@@ -4393,13 +4504,13 @@
         <v>16300</v>
       </c>
       <c r="AD49" s="3">
+        <v>16300</v>
+      </c>
+      <c r="AE49" s="3">
         <v>2500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2100</v>
-      </c>
-      <c r="AF49" s="3">
-        <v>1100</v>
       </c>
       <c r="AG49" s="3">
         <v>1100</v>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,16 +4720,19 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>100</v>
+      </c>
+      <c r="E52" s="3">
         <v>200</v>
-      </c>
-      <c r="E52" s="3">
-        <v>100</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
@@ -4633,13 +4753,13 @@
         <v>100</v>
       </c>
       <c r="L52" s="3">
+        <v>100</v>
+      </c>
+      <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>100</v>
-      </c>
-      <c r="N52" s="3">
-        <v>200</v>
       </c>
       <c r="O52" s="3">
         <v>200</v>
@@ -4657,22 +4777,22 @@
         <v>200</v>
       </c>
       <c r="T52" s="3">
+        <v>200</v>
+      </c>
+      <c r="U52" s="3">
         <v>300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>700</v>
-      </c>
-      <c r="V52" s="3">
-        <v>600</v>
       </c>
       <c r="W52" s="3">
         <v>600</v>
       </c>
       <c r="X52" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y52" s="3">
         <v>300</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>400</v>
       </c>
       <c r="Z52" s="3">
         <v>400</v>
@@ -4681,28 +4801,31 @@
         <v>400</v>
       </c>
       <c r="AB52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AC52" s="3">
         <v>500</v>
       </c>
       <c r="AD52" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE52" s="3">
         <v>15100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>15000</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>2100</v>
       </c>
       <c r="AG52" s="3">
         <v>2100</v>
       </c>
       <c r="AH52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AI52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E54" s="3">
         <v>28500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>29200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>29800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>28300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>30100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>30300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>30100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>35900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>38500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>41100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>40000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>39800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>40400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>49900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>50800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>51500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>52500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>50700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>56600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>55600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>24400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>23700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>23200</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,28 +5099,29 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E57" s="3">
         <v>4000</v>
-      </c>
-      <c r="E57" s="3">
-        <v>4500</v>
       </c>
       <c r="F57" s="3">
         <v>4500</v>
       </c>
       <c r="G57" s="3">
-        <v>4200</v>
+        <v>4500</v>
       </c>
       <c r="H57" s="3">
         <v>4200</v>
       </c>
       <c r="I57" s="3">
-        <v>3300</v>
+        <v>4200</v>
       </c>
       <c r="J57" s="3">
         <v>3300</v>
@@ -4999,87 +5130,90 @@
         <v>3300</v>
       </c>
       <c r="L57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="M57" s="3">
         <v>4400</v>
-      </c>
-      <c r="M57" s="3">
-        <v>3500</v>
       </c>
       <c r="N57" s="3">
         <v>3500</v>
       </c>
       <c r="O57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="P57" s="3">
         <v>2600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>6800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E58" s="3">
         <v>500</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>19</v>
+      <c r="F58" s="3">
+        <v>500</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>19</v>
@@ -5093,8 +5227,8 @@
       <c r="J58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -5112,40 +5246,40 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>800</v>
-      </c>
-      <c r="R58" s="3">
-        <v>200</v>
       </c>
       <c r="S58" s="3">
         <v>200</v>
       </c>
       <c r="T58" s="3">
+        <v>200</v>
+      </c>
+      <c r="U58" s="3">
         <v>1500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>900</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
       <c r="X58" s="3">
         <v>0</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>2000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2600</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>900</v>
       </c>
       <c r="AC58" s="3">
         <v>900</v>
@@ -5156,8 +5290,8 @@
       <c r="AE58" s="3">
         <v>900</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>19</v>
+      <c r="AF58" s="3">
+        <v>900</v>
       </c>
       <c r="AG58" s="3" t="s">
         <v>19</v>
@@ -5165,215 +5299,224 @@
       <c r="AH58" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E59" s="3">
         <v>6700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>4500</v>
       </c>
       <c r="K59" s="3">
         <v>4500</v>
       </c>
       <c r="L59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="M59" s="3">
         <v>4900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3900</v>
-      </c>
-      <c r="P59" s="3">
-        <v>3800</v>
       </c>
       <c r="Q59" s="3">
         <v>3800</v>
       </c>
       <c r="R59" s="3">
-        <v>4500</v>
+        <v>3800</v>
       </c>
       <c r="S59" s="3">
         <v>4500</v>
       </c>
       <c r="T59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="U59" s="3">
         <v>5200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E60" s="3">
         <v>11200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11600</v>
-      </c>
-      <c r="W60" s="3">
-        <v>10600</v>
       </c>
       <c r="X60" s="3">
         <v>10600</v>
       </c>
       <c r="Y60" s="3">
+        <v>10600</v>
+      </c>
+      <c r="Z60" s="3">
         <v>13200</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>11300</v>
       </c>
       <c r="AA60" s="3">
         <v>11300</v>
       </c>
       <c r="AB60" s="3">
+        <v>11300</v>
+      </c>
+      <c r="AC60" s="3">
         <v>11000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
         <v>200</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -5400,22 +5543,22 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>1900</v>
       </c>
       <c r="Q61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R61" s="3">
         <v>1000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>1700</v>
       </c>
       <c r="S61" s="3">
         <v>1700</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
@@ -5445,7 +5588,7 @@
         <v>0</v>
       </c>
       <c r="AD61" s="3">
-        <v>3100</v>
+        <v>0</v>
       </c>
       <c r="AE61" s="3">
         <v>3100</v>
@@ -5459,106 +5602,112 @@
       <c r="AH61" s="3">
         <v>3100</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E62" s="3">
         <v>3500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2500</v>
-      </c>
-      <c r="F62" s="3">
-        <v>2700</v>
       </c>
       <c r="G62" s="3">
         <v>2700</v>
       </c>
       <c r="H62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I62" s="3">
         <v>1300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3200</v>
-      </c>
-      <c r="O62" s="3">
-        <v>3500</v>
       </c>
       <c r="P62" s="3">
         <v>3500</v>
       </c>
       <c r="Q62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="R62" s="3">
         <v>3000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>10700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>10800</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>500</v>
       </c>
       <c r="AG62" s="3">
         <v>500</v>
       </c>
       <c r="AH62" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI62" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E66" s="3">
         <v>14800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>16300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>17800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>16200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>22100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>18700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>18800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>17400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>23800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>22900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>9700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>9200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,97 +6548,100 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-44000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-42900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-41000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-40600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-39800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-38300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-36900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-36600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-35700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-35800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-35900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-37400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-37800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-39500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-35500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-35200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-34600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-33400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-32900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-32300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-32000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-28700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-24300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-23700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-22900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-22800</v>
-      </c>
-      <c r="AD72" s="3">
-        <v>-23100</v>
       </c>
       <c r="AE72" s="3">
         <v>-23100</v>
       </c>
       <c r="AF72" s="3">
-        <v>-22800</v>
+        <v>-23100</v>
       </c>
       <c r="AG72" s="3">
         <v>-22800</v>
@@ -6475,8 +6649,11 @@
       <c r="AH72" s="3">
         <v>-22800</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3">
+        <v>-22800</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E76" s="3">
         <v>13700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>21300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>21500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>22100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>23300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>23700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>24200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>24600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>27800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>32100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>32600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>33300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>33200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>32900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>32700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-900</v>
-      </c>
-      <c r="L81" s="3">
-        <v>100</v>
       </c>
       <c r="M81" s="3">
         <v>100</v>
       </c>
       <c r="N81" s="3">
+        <v>100</v>
+      </c>
+      <c r="O81" s="3">
         <v>1500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-800</v>
       </c>
-      <c r="AB81" s="3">
-        <v>0</v>
-      </c>
       <c r="AC81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="3">
         <v>300</v>
       </c>
-      <c r="AD81" s="3">
-        <v>0</v>
-      </c>
       <c r="AE81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-300</v>
       </c>
-      <c r="AF81" s="3">
-        <v>0</v>
-      </c>
       <c r="AG81" s="3">
         <v>0</v>
       </c>
       <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7214,13 +7413,13 @@
         <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
         <v>200</v>
       </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
@@ -7268,7 +7467,7 @@
         <v>100</v>
       </c>
       <c r="X83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y83" s="3">
         <v>200</v>
@@ -7292,7 +7491,7 @@
         <v>200</v>
       </c>
       <c r="AF83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AG83" s="3">
         <v>100</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>200</v>
+        <v>-200</v>
       </c>
       <c r="E89" s="3">
         <v>200</v>
       </c>
       <c r="F89" s="3">
+        <v>200</v>
+      </c>
+      <c r="G89" s="3">
         <v>-1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1900</v>
-      </c>
-      <c r="M89" s="3">
-        <v>300</v>
       </c>
       <c r="N89" s="3">
         <v>300</v>
       </c>
       <c r="O89" s="3">
+        <v>300</v>
+      </c>
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,17 +8144,18 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
@@ -7948,7 +8169,7 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
@@ -7957,14 +8178,14 @@
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -7978,11 +8199,11 @@
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
@@ -7993,22 +8214,22 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-100</v>
       </c>
       <c r="AE91" s="3">
         <v>-100</v>
@@ -8020,10 +8241,13 @@
         <v>-100</v>
       </c>
       <c r="AH91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,47 +8445,50 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
@@ -8266,13 +8496,13 @@
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U94" s="3">
         <v>-100</v>
@@ -8281,43 +8511,46 @@
         <v>-100</v>
       </c>
       <c r="W94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>5000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>1400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>500</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>-100</v>
       </c>
       <c r="AG94" s="3">
         <v>-100</v>
       </c>
       <c r="AH94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8753,11 +8999,11 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
@@ -8786,64 +9032,67 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>1900</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>900</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1700</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
       <c r="AF100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG100" s="3">
         <v>100</v>
       </c>
       <c r="AH100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI100" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1000</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-2600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1900</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TGEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TGEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>TGEN</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E8" s="3">
         <v>4700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5000</v>
-      </c>
-      <c r="P8" s="3">
-        <v>6100</v>
       </c>
       <c r="Q8" s="3">
         <v>6100</v>
       </c>
       <c r="R8" s="3">
+        <v>6100</v>
+      </c>
+      <c r="S8" s="3">
         <v>5700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8000</v>
-      </c>
-      <c r="V8" s="3">
-        <v>8700</v>
       </c>
       <c r="W8" s="3">
         <v>8700</v>
       </c>
       <c r="X8" s="3">
+        <v>8700</v>
+      </c>
+      <c r="Y8" s="3">
         <v>7900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E9" s="3">
         <v>2600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2200</v>
-      </c>
-      <c r="K9" s="3">
-        <v>3700</v>
       </c>
       <c r="L9" s="3">
         <v>3700</v>
       </c>
       <c r="M9" s="3">
+        <v>3700</v>
+      </c>
+      <c r="N9" s="3">
         <v>4300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>6300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>6500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E10" s="3">
         <v>2100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="M10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="N10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="O10" s="3">
+        <v>3500</v>
+      </c>
+      <c r="P10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="R10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="S10" s="3">
         <v>2400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="T10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="U10" s="3">
         <v>2900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="V10" s="3">
         <v>2800</v>
       </c>
-      <c r="I10" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>2300</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="W10" s="3">
+        <v>3300</v>
+      </c>
+      <c r="X10" s="3">
         <v>2900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="Y10" s="3">
+        <v>3500</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AI10" s="3">
         <v>2700</v>
       </c>
-      <c r="M10" s="3">
-        <v>3100</v>
-      </c>
-      <c r="N10" s="3">
-        <v>3500</v>
-      </c>
-      <c r="O10" s="3">
-        <v>2300</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="AJ10" s="3">
         <v>2800</v>
       </c>
-      <c r="Q10" s="3">
-        <v>3000</v>
-      </c>
-      <c r="R10" s="3">
-        <v>2400</v>
-      </c>
-      <c r="S10" s="3">
-        <v>2800</v>
-      </c>
-      <c r="T10" s="3">
-        <v>2900</v>
-      </c>
-      <c r="U10" s="3">
-        <v>2800</v>
-      </c>
-      <c r="V10" s="3">
-        <v>3300</v>
-      </c>
-      <c r="W10" s="3">
-        <v>2900</v>
-      </c>
-      <c r="X10" s="3">
-        <v>3500</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>3000</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>3700</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>2800</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>3200</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>3900</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>3800</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>3300</v>
-      </c>
-      <c r="AF10" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>2900</v>
-      </c>
-      <c r="AH10" s="3">
-        <v>2700</v>
-      </c>
-      <c r="AI10" s="3">
-        <v>2800</v>
-      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1148,10 +1162,10 @@
         <v>200</v>
       </c>
       <c r="E12" s="3">
+        <v>200</v>
+      </c>
+      <c r="F12" s="3">
         <v>300</v>
-      </c>
-      <c r="F12" s="3">
-        <v>200</v>
       </c>
       <c r="G12" s="3">
         <v>200</v>
@@ -1172,13 +1186,13 @@
         <v>200</v>
       </c>
       <c r="M12" s="3">
+        <v>200</v>
+      </c>
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>200</v>
-      </c>
-      <c r="O12" s="3">
-        <v>100</v>
       </c>
       <c r="P12" s="3">
         <v>100</v>
@@ -1193,10 +1207,10 @@
         <v>100</v>
       </c>
       <c r="T12" s="3">
+        <v>100</v>
+      </c>
+      <c r="U12" s="3">
         <v>200</v>
-      </c>
-      <c r="U12" s="3">
-        <v>400</v>
       </c>
       <c r="V12" s="3">
         <v>400</v>
@@ -1208,7 +1222,7 @@
         <v>400</v>
       </c>
       <c r="Y12" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Z12" s="3">
         <v>300</v>
@@ -1217,16 +1231,16 @@
         <v>300</v>
       </c>
       <c r="AB12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC12" s="3">
         <v>400</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>300</v>
       </c>
       <c r="AD12" s="3">
         <v>300</v>
       </c>
       <c r="AE12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AF12" s="3">
         <v>200</v>
@@ -1235,13 +1249,16 @@
         <v>200</v>
       </c>
       <c r="AH12" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI12" s="3">
         <v>100</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,82 +1358,85 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>100</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>-700</v>
+      </c>
+      <c r="R14" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="S14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="T14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="P14" s="3">
-        <v>-700</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="R14" s="3">
-        <v>2900</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>19</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z14" s="3">
         <v>3700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>4400</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>19</v>
@@ -1433,8 +1453,8 @@
       <c r="AF14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1442,31 +1462,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E17" s="3">
         <v>6200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7700</v>
-      </c>
-      <c r="G17" s="3">
-        <v>7500</v>
       </c>
       <c r="H17" s="3">
         <v>7500</v>
       </c>
       <c r="I17" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J17" s="3">
         <v>6800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9100</v>
-      </c>
-      <c r="V17" s="3">
-        <v>9200</v>
       </c>
       <c r="W17" s="3">
         <v>9200</v>
       </c>
       <c r="X17" s="3">
+        <v>9200</v>
+      </c>
+      <c r="Y17" s="3">
         <v>8200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>11500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>13700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1500</v>
       </c>
-      <c r="E18" s="3">
-        <v>-1000</v>
-      </c>
       <c r="F18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G18" s="3">
         <v>-1800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1400</v>
       </c>
       <c r="J18" s="3">
         <v>-1400</v>
       </c>
       <c r="K18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="L18" s="3">
         <v>-200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-800</v>
       </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
       <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
         <v>200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1100</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-500</v>
       </c>
       <c r="W18" s="3">
         <v>-500</v>
       </c>
       <c r="X18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-600</v>
       </c>
       <c r="AB18" s="3">
         <v>-600</v>
       </c>
       <c r="AC18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AD18" s="3">
         <v>100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-200</v>
       </c>
-      <c r="AG18" s="3">
-        <v>0</v>
-      </c>
       <c r="AH18" s="3">
         <v>0</v>
       </c>
       <c r="AI18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1816,8 +1849,9 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1831,74 +1865,74 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>100</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
@@ -1917,109 +1951,115 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-1400</v>
+        <v>-800</v>
       </c>
       <c r="E21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1700</v>
       </c>
-      <c r="G21" s="3">
-        <v>-300</v>
-      </c>
       <c r="H21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I21" s="3">
         <v>-600</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-1300</v>
       </c>
       <c r="J21" s="3">
         <v>-1300</v>
       </c>
       <c r="K21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="L21" s="3">
         <v>-100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-700</v>
-      </c>
-      <c r="M21" s="3">
-        <v>200</v>
       </c>
       <c r="N21" s="3">
         <v>200</v>
       </c>
       <c r="O21" s="3">
+        <v>200</v>
+      </c>
+      <c r="P21" s="3">
         <v>1600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1000</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-400</v>
       </c>
       <c r="W21" s="3">
         <v>-400</v>
       </c>
       <c r="X21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-100</v>
-      </c>
-      <c r="AG21" s="3">
-        <v>100</v>
       </c>
       <c r="AH21" s="3">
         <v>100</v>
       </c>
       <c r="AI21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2072,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U22" s="3">
         <v>100</v>
       </c>
       <c r="V22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -2090,11 +2130,11 @@
         <v>0</v>
       </c>
       <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
         <v>100</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
@@ -2119,114 +2159,120 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-800</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-1400</v>
       </c>
       <c r="J23" s="3">
         <v>-1400</v>
       </c>
       <c r="K23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="L23" s="3">
         <v>-200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-800</v>
-      </c>
-      <c r="M23" s="3">
-        <v>100</v>
       </c>
       <c r="N23" s="3">
         <v>100</v>
       </c>
       <c r="O23" s="3">
+        <v>100</v>
+      </c>
+      <c r="P23" s="3">
         <v>1500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-700</v>
       </c>
-      <c r="AC23" s="3">
-        <v>0</v>
-      </c>
       <c r="AD23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="3">
         <v>300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-300</v>
       </c>
-      <c r="AG23" s="3">
-        <v>0</v>
-      </c>
       <c r="AH23" s="3">
         <v>0</v>
       </c>
       <c r="AI23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -2237,8 +2283,8 @@
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
@@ -2300,14 +2346,14 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-      <c r="AC24" s="3" t="s">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="3" t="s">
-        <v>19</v>
+      <c r="AE24" s="3">
+        <v>0</v>
       </c>
       <c r="AF24" s="3" t="s">
         <v>19</v>
@@ -2321,8 +2367,11 @@
       <c r="AI24" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="AJ24" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-800</v>
-      </c>
-      <c r="M26" s="3">
-        <v>100</v>
       </c>
       <c r="N26" s="3">
         <v>100</v>
       </c>
       <c r="O26" s="3">
+        <v>100</v>
+      </c>
+      <c r="P26" s="3">
         <v>1500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-700</v>
       </c>
-      <c r="AC26" s="3">
-        <v>0</v>
-      </c>
       <c r="AD26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="3">
         <v>300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-300</v>
       </c>
-      <c r="AG26" s="3">
-        <v>0</v>
-      </c>
       <c r="AH26" s="3">
         <v>0</v>
       </c>
       <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-900</v>
-      </c>
-      <c r="M27" s="3">
-        <v>100</v>
       </c>
       <c r="N27" s="3">
         <v>100</v>
       </c>
       <c r="O27" s="3">
+        <v>100</v>
+      </c>
+      <c r="P27" s="3">
         <v>1500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-800</v>
       </c>
-      <c r="AC27" s="3">
-        <v>0</v>
-      </c>
       <c r="AD27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="3">
         <v>300</v>
       </c>
-      <c r="AE27" s="3">
-        <v>0</v>
-      </c>
       <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-300</v>
       </c>
-      <c r="AG27" s="3">
-        <v>0</v>
-      </c>
       <c r="AH27" s="3">
         <v>0</v>
       </c>
       <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,8 +3095,11 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3043,74 +3113,74 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>100</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
@@ -3129,109 +3199,115 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-900</v>
-      </c>
-      <c r="M33" s="3">
-        <v>100</v>
       </c>
       <c r="N33" s="3">
         <v>100</v>
       </c>
       <c r="O33" s="3">
+        <v>100</v>
+      </c>
+      <c r="P33" s="3">
         <v>1500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-800</v>
       </c>
-      <c r="AC33" s="3">
-        <v>0</v>
-      </c>
       <c r="AD33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="3">
         <v>300</v>
       </c>
-      <c r="AE33" s="3">
-        <v>0</v>
-      </c>
       <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-300</v>
       </c>
-      <c r="AG33" s="3">
-        <v>0</v>
-      </c>
       <c r="AH33" s="3">
         <v>0</v>
       </c>
       <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-900</v>
-      </c>
-      <c r="M35" s="3">
-        <v>100</v>
       </c>
       <c r="N35" s="3">
         <v>100</v>
       </c>
       <c r="O35" s="3">
+        <v>100</v>
+      </c>
+      <c r="P35" s="3">
         <v>1500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-800</v>
       </c>
-      <c r="AC35" s="3">
-        <v>0</v>
-      </c>
       <c r="AD35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="3">
         <v>300</v>
       </c>
-      <c r="AE35" s="3">
-        <v>0</v>
-      </c>
       <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-300</v>
       </c>
-      <c r="AG35" s="3">
-        <v>0</v>
-      </c>
       <c r="AH35" s="3">
         <v>0</v>
       </c>
       <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E41" s="3">
         <v>800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2900</v>
-      </c>
-      <c r="U41" s="3">
-        <v>900</v>
       </c>
       <c r="V41" s="3">
         <v>900</v>
       </c>
       <c r="W41" s="3">
+        <v>900</v>
+      </c>
+      <c r="X41" s="3">
         <v>800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,8 +3904,11 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3823,186 +3916,189 @@
         <v>6600</v>
       </c>
       <c r="E43" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F43" s="3">
         <v>7800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>14300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>13000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>17100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>20000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>18100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>17500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>16900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>19100</v>
-      </c>
-      <c r="AA43" s="3">
-        <v>16000</v>
       </c>
       <c r="AB43" s="3">
         <v>16000</v>
       </c>
       <c r="AC43" s="3">
+        <v>16000</v>
+      </c>
+      <c r="AD43" s="3">
         <v>16500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>14100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>14700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>12500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>11800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>11200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E44" s="3">
         <v>10100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>10600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>11000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>12000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>11900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>10500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8200</v>
-      </c>
-      <c r="M44" s="3">
-        <v>7800</v>
       </c>
       <c r="N44" s="3">
         <v>7800</v>
       </c>
       <c r="O44" s="3">
+        <v>7800</v>
+      </c>
+      <c r="P44" s="3">
         <v>7900</v>
-      </c>
-      <c r="P44" s="3">
-        <v>6800</v>
       </c>
       <c r="Q44" s="3">
         <v>6800</v>
       </c>
       <c r="R44" s="3">
+        <v>6800</v>
+      </c>
+      <c r="S44" s="3">
         <v>7200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>7300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>7500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>7100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>7000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>6700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>6300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5500</v>
-      </c>
-      <c r="AC44" s="3">
-        <v>5100</v>
       </c>
       <c r="AD44" s="3">
         <v>5100</v>
       </c>
       <c r="AE44" s="3">
-        <v>6100</v>
+        <v>5100</v>
       </c>
       <c r="AF44" s="3">
         <v>6100</v>
@@ -4011,42 +4107,45 @@
         <v>6100</v>
       </c>
       <c r="AH44" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AI44" s="3">
         <v>4800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K45" s="3">
+        <v>400</v>
+      </c>
+      <c r="L45" s="3">
         <v>500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>400</v>
-      </c>
-      <c r="K45" s="3">
-        <v>500</v>
-      </c>
-      <c r="L45" s="3">
-        <v>600</v>
       </c>
       <c r="M45" s="3">
         <v>600</v>
@@ -4058,19 +4157,19 @@
         <v>600</v>
       </c>
       <c r="P45" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q45" s="3">
         <v>800</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>600</v>
       </c>
       <c r="R45" s="3">
         <v>600</v>
       </c>
       <c r="S45" s="3">
+        <v>600</v>
+      </c>
+      <c r="T45" s="3">
         <v>500</v>
-      </c>
-      <c r="T45" s="3">
-        <v>600</v>
       </c>
       <c r="U45" s="3">
         <v>600</v>
@@ -4088,152 +4187,158 @@
         <v>600</v>
       </c>
       <c r="Z45" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA45" s="3">
         <v>700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>800</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>900</v>
       </c>
       <c r="AC45" s="3">
         <v>900</v>
       </c>
       <c r="AD45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE45" s="3">
         <v>800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E46" s="3">
         <v>18100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>20300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22000</v>
-      </c>
-      <c r="K46" s="3">
-        <v>23400</v>
       </c>
       <c r="L46" s="3">
         <v>23400</v>
       </c>
       <c r="M46" s="3">
+        <v>23400</v>
+      </c>
+      <c r="N46" s="3">
         <v>25600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>24700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>23200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>23300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>22200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>23600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>23800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>26100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>27900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>26600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>26200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>26800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>26400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>22900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>23400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>23700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>21700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>23600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>22700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>20600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>20100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="3">
         <v>100</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="F47" s="3">
         <v>100</v>
       </c>
-      <c r="G47" s="3">
-        <v>100</v>
+      <c r="G47" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="H47" s="3">
         <v>100</v>
@@ -4250,8 +4355,8 @@
       <c r="L47" s="3">
         <v>100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>19</v>
+      <c r="M47" s="3">
+        <v>100</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>19</v>
@@ -4268,8 +4373,8 @@
       <c r="R47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -4310,109 +4415,112 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>19</v>
+      <c r="AG47" s="3">
+        <v>0</v>
       </c>
       <c r="AH47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AI47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>15500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>15700</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>500</v>
       </c>
       <c r="AH48" s="3">
         <v>500</v>
@@ -4420,34 +4528,37 @@
       <c r="AI48" s="3">
         <v>500</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E49" s="3">
         <v>5300</v>
-      </c>
-      <c r="E49" s="3">
-        <v>5200</v>
       </c>
       <c r="F49" s="3">
         <v>5200</v>
       </c>
       <c r="G49" s="3">
+        <v>5200</v>
+      </c>
+      <c r="H49" s="3">
         <v>5400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5600</v>
-      </c>
-      <c r="I49" s="3">
-        <v>3400</v>
       </c>
       <c r="J49" s="3">
         <v>3400</v>
       </c>
       <c r="K49" s="3">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="L49" s="3">
         <v>3500</v>
@@ -4456,46 +4567,46 @@
         <v>3500</v>
       </c>
       <c r="N49" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="O49" s="3">
         <v>3600</v>
       </c>
       <c r="P49" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="Q49" s="3">
         <v>3700</v>
       </c>
       <c r="R49" s="3">
+        <v>3700</v>
+      </c>
+      <c r="S49" s="3">
         <v>3800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6700</v>
-      </c>
-      <c r="V49" s="3">
-        <v>6900</v>
       </c>
       <c r="W49" s="3">
         <v>6900</v>
       </c>
       <c r="X49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Y49" s="3">
         <v>6800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>11900</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>16300</v>
       </c>
       <c r="AB49" s="3">
         <v>16300</v>
@@ -4507,13 +4618,13 @@
         <v>16300</v>
       </c>
       <c r="AE49" s="3">
+        <v>16300</v>
+      </c>
+      <c r="AF49" s="3">
         <v>2500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2100</v>
-      </c>
-      <c r="AG49" s="3">
-        <v>1100</v>
       </c>
       <c r="AH49" s="3">
         <v>1100</v>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>1100</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>1100</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,22 +4840,25 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>200</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
@@ -4756,13 +4876,13 @@
         <v>100</v>
       </c>
       <c r="M52" s="3">
+        <v>100</v>
+      </c>
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>100</v>
-      </c>
-      <c r="O52" s="3">
-        <v>200</v>
       </c>
       <c r="P52" s="3">
         <v>200</v>
@@ -4780,22 +4900,22 @@
         <v>200</v>
       </c>
       <c r="U52" s="3">
+        <v>200</v>
+      </c>
+      <c r="V52" s="3">
         <v>300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>700</v>
-      </c>
-      <c r="W52" s="3">
-        <v>600</v>
       </c>
       <c r="X52" s="3">
         <v>600</v>
       </c>
       <c r="Y52" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z52" s="3">
         <v>300</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>400</v>
       </c>
       <c r="AA52" s="3">
         <v>400</v>
@@ -4804,28 +4924,31 @@
         <v>400</v>
       </c>
       <c r="AC52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AD52" s="3">
         <v>500</v>
       </c>
       <c r="AE52" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF52" s="3">
         <v>15100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>15000</v>
-      </c>
-      <c r="AG52" s="3">
-        <v>2100</v>
       </c>
       <c r="AH52" s="3">
         <v>2100</v>
       </c>
       <c r="AI52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E54" s="3">
         <v>27200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>28500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>29200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>29800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>28200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>28300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>30100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>30300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>30100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>35200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>35900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>38500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>41100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>40000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>39800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>40400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>49900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>50800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>51500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>52500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>50700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>56600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>55600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>24400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>23700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>23200</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,31 +5230,32 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E57" s="3">
         <v>4400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>4500</v>
       </c>
       <c r="G57" s="3">
         <v>4500</v>
       </c>
       <c r="H57" s="3">
-        <v>4200</v>
+        <v>4500</v>
       </c>
       <c r="I57" s="3">
         <v>4200</v>
       </c>
       <c r="J57" s="3">
-        <v>3300</v>
+        <v>4200</v>
       </c>
       <c r="K57" s="3">
         <v>3300</v>
@@ -5133,105 +5264,108 @@
         <v>3300</v>
       </c>
       <c r="M57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N57" s="3">
         <v>4400</v>
-      </c>
-      <c r="N57" s="3">
-        <v>3500</v>
       </c>
       <c r="O57" s="3">
         <v>3500</v>
       </c>
       <c r="P57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="Q57" s="3">
         <v>2600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>7200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>6800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G58" s="3">
+        <v>800</v>
+      </c>
+      <c r="H58" s="3">
+        <v>400</v>
+      </c>
+      <c r="I58" s="3">
+        <v>500</v>
+      </c>
+      <c r="J58" s="3">
         <v>600</v>
-      </c>
-      <c r="E58" s="3">
-        <v>500</v>
-      </c>
-      <c r="F58" s="3">
-        <v>500</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5249,40 +5383,40 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>800</v>
-      </c>
-      <c r="S58" s="3">
-        <v>200</v>
       </c>
       <c r="T58" s="3">
         <v>200</v>
       </c>
       <c r="U58" s="3">
+        <v>200</v>
+      </c>
+      <c r="V58" s="3">
         <v>1500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>900</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
       <c r="Y58" s="3">
         <v>0</v>
       </c>
       <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>2000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2600</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>900</v>
       </c>
       <c r="AD58" s="3">
         <v>900</v>
@@ -5293,8 +5427,8 @@
       <c r="AF58" s="3">
         <v>900</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>19</v>
+      <c r="AG58" s="3">
+        <v>900</v>
       </c>
       <c r="AH58" s="3" t="s">
         <v>19</v>
@@ -5302,233 +5436,242 @@
       <c r="AI58" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6500</v>
+        <v>2300</v>
       </c>
       <c r="E59" s="3">
-        <v>6700</v>
+        <v>3600</v>
       </c>
       <c r="F59" s="3">
-        <v>5400</v>
+        <v>3600</v>
       </c>
       <c r="G59" s="3">
-        <v>5600</v>
+        <v>2800</v>
       </c>
       <c r="H59" s="3">
-        <v>6000</v>
+        <v>2600</v>
       </c>
       <c r="I59" s="3">
-        <v>5200</v>
+        <v>2900</v>
       </c>
       <c r="J59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K59" s="3">
         <v>4400</v>
-      </c>
-      <c r="K59" s="3">
-        <v>4500</v>
       </c>
       <c r="L59" s="3">
         <v>4500</v>
       </c>
       <c r="M59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="N59" s="3">
         <v>4900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3900</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>3800</v>
       </c>
       <c r="R59" s="3">
         <v>3800</v>
       </c>
       <c r="S59" s="3">
-        <v>4500</v>
+        <v>3800</v>
       </c>
       <c r="T59" s="3">
         <v>4500</v>
       </c>
       <c r="U59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="V59" s="3">
         <v>5200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E60" s="3">
         <v>11500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>13400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11600</v>
-      </c>
-      <c r="X60" s="3">
-        <v>10600</v>
       </c>
       <c r="Y60" s="3">
         <v>10600</v>
       </c>
       <c r="Z60" s="3">
+        <v>10600</v>
+      </c>
+      <c r="AA60" s="3">
         <v>13200</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>11300</v>
       </c>
       <c r="AB60" s="3">
         <v>11300</v>
       </c>
       <c r="AC60" s="3">
+        <v>11300</v>
+      </c>
+      <c r="AD60" s="3">
         <v>11000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>9400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>1800</v>
       </c>
       <c r="E61" s="3">
-        <v>200</v>
+        <v>1700</v>
       </c>
       <c r="F61" s="3">
-        <v>200</v>
+        <v>1700</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5546,22 +5689,22 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>1900</v>
       </c>
       <c r="R61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="S61" s="3">
         <v>1000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>1700</v>
       </c>
       <c r="T61" s="3">
         <v>1700</v>
       </c>
       <c r="U61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="V61" s="3">
         <v>0</v>
@@ -5591,7 +5734,7 @@
         <v>0</v>
       </c>
       <c r="AE61" s="3">
-        <v>3100</v>
+        <v>0</v>
       </c>
       <c r="AF61" s="3">
         <v>3100</v>
@@ -5605,109 +5748,115 @@
       <c r="AI61" s="3">
         <v>3100</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>3100</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3400</v>
+        <v>1500</v>
       </c>
       <c r="E62" s="3">
-        <v>3500</v>
+        <v>1600</v>
       </c>
       <c r="F62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J62" s="3">
+        <v>500</v>
+      </c>
+      <c r="K62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O62" s="3">
         <v>2500</v>
       </c>
-      <c r="G62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="H62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J62" s="3">
-        <v>1600</v>
-      </c>
-      <c r="K62" s="3">
-        <v>1900</v>
-      </c>
-      <c r="L62" s="3">
-        <v>2100</v>
-      </c>
-      <c r="M62" s="3">
-        <v>2200</v>
-      </c>
-      <c r="N62" s="3">
-        <v>2500</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3200</v>
-      </c>
-      <c r="P62" s="3">
-        <v>3500</v>
       </c>
       <c r="Q62" s="3">
         <v>3500</v>
       </c>
       <c r="R62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="S62" s="3">
         <v>3000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>8300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>10700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>10800</v>
-      </c>
-      <c r="AG62" s="3">
-        <v>500</v>
       </c>
       <c r="AH62" s="3">
         <v>500</v>
       </c>
       <c r="AI62" s="3">
+        <v>500</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>15000</v>
+        <v>16300</v>
       </c>
       <c r="E66" s="3">
+        <v>15100</v>
+      </c>
+      <c r="F66" s="3">
         <v>14800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
+        <v>13100</v>
+      </c>
+      <c r="H66" s="3">
+        <v>12800</v>
+      </c>
+      <c r="I66" s="3">
         <v>13000</v>
       </c>
-      <c r="G66" s="3">
-        <v>12700</v>
-      </c>
-      <c r="H66" s="3">
-        <v>12900</v>
-      </c>
-      <c r="I66" s="3">
-        <v>10600</v>
-      </c>
       <c r="J66" s="3">
+        <v>10700</v>
+      </c>
+      <c r="K66" s="3">
         <v>9200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>17800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>22100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>18700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>18800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>17400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>23800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>22900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>9700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,100 +6722,103 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-46500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-45500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-44000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-42900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-41000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-40600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-39800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-38300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-36900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-36600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-35700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-35800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-35900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-37400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-37800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-39500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-35500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-35200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-34600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-33400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-32900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-32300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-32000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-28700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-24300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-23700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-22900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-22800</v>
-      </c>
-      <c r="AE72" s="3">
-        <v>-23100</v>
       </c>
       <c r="AF72" s="3">
         <v>-23100</v>
       </c>
       <c r="AG72" s="3">
-        <v>-22800</v>
+        <v>-23100</v>
       </c>
       <c r="AH72" s="3">
         <v>-22800</v>
@@ -6652,8 +6826,11 @@
       <c r="AI72" s="3">
         <v>-22800</v>
       </c>
+      <c r="AJ72" s="3">
+        <v>-22800</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E76" s="3">
         <v>12200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>21300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>21500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>22100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>23300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>23700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>24200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>24600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>27800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>32100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>32600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>33300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>33200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>32900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>32700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-900</v>
-      </c>
-      <c r="M81" s="3">
-        <v>100</v>
       </c>
       <c r="N81" s="3">
         <v>100</v>
       </c>
       <c r="O81" s="3">
+        <v>100</v>
+      </c>
+      <c r="P81" s="3">
         <v>1500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-800</v>
       </c>
-      <c r="AC81" s="3">
-        <v>0</v>
-      </c>
       <c r="AD81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="3">
         <v>300</v>
       </c>
-      <c r="AE81" s="3">
-        <v>0</v>
-      </c>
       <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-300</v>
       </c>
-      <c r="AG81" s="3">
-        <v>0</v>
-      </c>
       <c r="AH81" s="3">
         <v>0</v>
       </c>
       <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,13 +7599,14 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
@@ -7416,10 +7615,10 @@
         <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
@@ -7470,7 +7669,7 @@
         <v>100</v>
       </c>
       <c r="Y83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z83" s="3">
         <v>200</v>
@@ -7494,7 +7693,7 @@
         <v>200</v>
       </c>
       <c r="AG83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AH83" s="3">
         <v>100</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>100</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,8 +8221,11 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8016,100 +8233,103 @@
         <v>-200</v>
       </c>
       <c r="E89" s="3">
-        <v>200</v>
+        <v>-200</v>
       </c>
       <c r="F89" s="3">
         <v>200</v>
       </c>
       <c r="G89" s="3">
+        <v>200</v>
+      </c>
+      <c r="H89" s="3">
         <v>-1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1900</v>
-      </c>
-      <c r="N89" s="3">
-        <v>300</v>
       </c>
       <c r="O89" s="3">
         <v>300</v>
       </c>
       <c r="P89" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,20 +8365,21 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
@@ -8168,11 +8389,11 @@
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="J91" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="K91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
@@ -8181,14 +8402,14 @@
         <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -8202,11 +8423,11 @@
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
@@ -8217,22 +8438,22 @@
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-100</v>
       </c>
       <c r="AF91" s="3">
         <v>-100</v>
@@ -8244,10 +8465,13 @@
         <v>-100</v>
       </c>
       <c r="AI91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,64 +8675,67 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="E94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V94" s="3">
         <v>-100</v>
@@ -8514,43 +8744,46 @@
         <v>-100</v>
       </c>
       <c r="X94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>5000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>500</v>
-      </c>
-      <c r="AG94" s="3">
-        <v>-100</v>
       </c>
       <c r="AH94" s="3">
         <v>-100</v>
       </c>
       <c r="AI94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,31 +9233,34 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="J100" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -9035,87 +9281,90 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>1900</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>900</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1700</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
         <v>0</v>
       </c>
       <c r="AG100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH100" s="3">
         <v>100</v>
       </c>
       <c r="AI100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1000</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-2600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1900</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TGEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TGEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>TGEN</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E8" s="3">
         <v>5600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5000</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>6100</v>
       </c>
       <c r="R8" s="3">
         <v>6100</v>
       </c>
       <c r="S8" s="3">
+        <v>6100</v>
+      </c>
+      <c r="T8" s="3">
         <v>5700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8000</v>
-      </c>
-      <c r="W8" s="3">
-        <v>8700</v>
       </c>
       <c r="X8" s="3">
         <v>8700</v>
       </c>
       <c r="Y8" s="3">
+        <v>8700</v>
+      </c>
+      <c r="Z8" s="3">
         <v>7900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>8500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E9" s="3">
         <v>3100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2200</v>
-      </c>
-      <c r="L9" s="3">
-        <v>3700</v>
       </c>
       <c r="M9" s="3">
         <v>3700</v>
       </c>
       <c r="N9" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O9" s="3">
         <v>4300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>6300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E10" s="3">
         <v>2500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1165,10 +1178,10 @@
         <v>200</v>
       </c>
       <c r="F12" s="3">
+        <v>200</v>
+      </c>
+      <c r="G12" s="3">
         <v>300</v>
-      </c>
-      <c r="G12" s="3">
-        <v>200</v>
       </c>
       <c r="H12" s="3">
         <v>200</v>
@@ -1189,13 +1202,13 @@
         <v>200</v>
       </c>
       <c r="N12" s="3">
+        <v>200</v>
+      </c>
+      <c r="O12" s="3">
         <v>100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>200</v>
-      </c>
-      <c r="P12" s="3">
-        <v>100</v>
       </c>
       <c r="Q12" s="3">
         <v>100</v>
@@ -1210,10 +1223,10 @@
         <v>100</v>
       </c>
       <c r="U12" s="3">
+        <v>100</v>
+      </c>
+      <c r="V12" s="3">
         <v>200</v>
-      </c>
-      <c r="V12" s="3">
-        <v>400</v>
       </c>
       <c r="W12" s="3">
         <v>400</v>
@@ -1225,7 +1238,7 @@
         <v>400</v>
       </c>
       <c r="Z12" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AA12" s="3">
         <v>300</v>
@@ -1234,16 +1247,16 @@
         <v>300</v>
       </c>
       <c r="AC12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD12" s="3">
         <v>400</v>
-      </c>
-      <c r="AD12" s="3">
-        <v>300</v>
       </c>
       <c r="AE12" s="3">
         <v>300</v>
       </c>
       <c r="AF12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AG12" s="3">
         <v>200</v>
@@ -1252,13 +1265,16 @@
         <v>200</v>
       </c>
       <c r="AI12" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ12" s="3">
         <v>100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1361,13 +1377,16 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1379,17 +1398,17 @@
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1403,43 +1422,43 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-1900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2900</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>19</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA14" s="3">
         <v>3700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>4400</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>19</v>
@@ -1456,8 +1475,8 @@
       <c r="AG14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
@@ -1465,8 +1484,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1483,17 +1505,17 @@
         <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
         <v>200</v>
       </c>
       <c r="J15" s="3">
+        <v>200</v>
+      </c>
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,112 +1629,116 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7700</v>
-      </c>
-      <c r="H17" s="3">
-        <v>7500</v>
       </c>
       <c r="I17" s="3">
         <v>7500</v>
       </c>
       <c r="J17" s="3">
+        <v>7500</v>
+      </c>
+      <c r="K17" s="3">
         <v>6800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9100</v>
-      </c>
-      <c r="W17" s="3">
-        <v>9200</v>
       </c>
       <c r="X17" s="3">
         <v>9200</v>
       </c>
       <c r="Y17" s="3">
+        <v>9200</v>
+      </c>
+      <c r="Z17" s="3">
         <v>8200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>11500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>7100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1717,103 +1746,106 @@
         <v>-900</v>
       </c>
       <c r="E18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-800</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-1400</v>
       </c>
       <c r="K18" s="3">
         <v>-1400</v>
       </c>
       <c r="L18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="M18" s="3">
         <v>-200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-800</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
       <c r="O18" s="3">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
         <v>200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1100</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-500</v>
       </c>
       <c r="X18" s="3">
         <v>-500</v>
       </c>
       <c r="Y18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-600</v>
       </c>
       <c r="AC18" s="3">
         <v>-600</v>
       </c>
       <c r="AD18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AE18" s="3">
         <v>100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-200</v>
       </c>
-      <c r="AH18" s="3">
-        <v>0</v>
-      </c>
       <c r="AI18" s="3">
         <v>0</v>
       </c>
       <c r="AJ18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1850,8 +1882,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1886,26 +1919,26 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1922,20 +1955,20 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
@@ -1954,8 +1987,11 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1963,103 +1999,106 @@
         <v>-800</v>
       </c>
       <c r="E21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-600</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-1300</v>
       </c>
       <c r="K21" s="3">
         <v>-1300</v>
       </c>
       <c r="L21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="M21" s="3">
         <v>-100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-700</v>
-      </c>
-      <c r="N21" s="3">
-        <v>200</v>
       </c>
       <c r="O21" s="3">
         <v>200</v>
       </c>
       <c r="P21" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q21" s="3">
         <v>1600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1000</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-400</v>
       </c>
       <c r="X21" s="3">
         <v>-400</v>
       </c>
       <c r="Y21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-100</v>
-      </c>
-      <c r="AH21" s="3">
-        <v>100</v>
       </c>
       <c r="AI21" s="3">
         <v>100</v>
       </c>
       <c r="AJ21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2115,13 +2154,13 @@
         <v>0</v>
       </c>
       <c r="U22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V22" s="3">
         <v>100</v>
       </c>
       <c r="W22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -2133,11 +2172,11 @@
         <v>0</v>
       </c>
       <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
         <v>100</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
@@ -2162,133 +2201,139 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-800</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-1400</v>
       </c>
       <c r="K23" s="3">
         <v>-1400</v>
       </c>
       <c r="L23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="M23" s="3">
         <v>-200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-800</v>
-      </c>
-      <c r="N23" s="3">
-        <v>100</v>
       </c>
       <c r="O23" s="3">
         <v>100</v>
       </c>
       <c r="P23" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="3">
         <v>1500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-700</v>
       </c>
-      <c r="AD23" s="3">
-        <v>0</v>
-      </c>
       <c r="AE23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="3">
         <v>300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-300</v>
       </c>
-      <c r="AH23" s="3">
-        <v>0</v>
-      </c>
       <c r="AI23" s="3">
         <v>0</v>
       </c>
       <c r="AJ23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -2349,14 +2394,14 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-      <c r="AD24" s="3" t="s">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="3" t="s">
-        <v>19</v>
+      <c r="AF24" s="3">
+        <v>0</v>
       </c>
       <c r="AG24" s="3" t="s">
         <v>19</v>
@@ -2370,8 +2415,11 @@
       <c r="AJ24" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="AK24" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-800</v>
-      </c>
-      <c r="N26" s="3">
-        <v>100</v>
       </c>
       <c r="O26" s="3">
         <v>100</v>
       </c>
       <c r="P26" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q26" s="3">
         <v>1500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-700</v>
       </c>
-      <c r="AD26" s="3">
-        <v>0</v>
-      </c>
       <c r="AE26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="3">
         <v>300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-300</v>
       </c>
-      <c r="AH26" s="3">
-        <v>0</v>
-      </c>
       <c r="AI26" s="3">
         <v>0</v>
       </c>
       <c r="AJ26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-900</v>
-      </c>
-      <c r="N27" s="3">
-        <v>100</v>
       </c>
       <c r="O27" s="3">
         <v>100</v>
       </c>
       <c r="P27" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q27" s="3">
         <v>1500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-800</v>
       </c>
-      <c r="AD27" s="3">
-        <v>0</v>
-      </c>
       <c r="AE27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="3">
         <v>300</v>
       </c>
-      <c r="AF27" s="3">
-        <v>0</v>
-      </c>
       <c r="AG27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="3">
         <v>-300</v>
       </c>
-      <c r="AH27" s="3">
-        <v>0</v>
-      </c>
       <c r="AI27" s="3">
         <v>0</v>
       </c>
       <c r="AJ27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3164,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3134,26 +3203,26 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -3170,20 +3239,20 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>100</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
@@ -3202,112 +3271,118 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-900</v>
-      </c>
-      <c r="N33" s="3">
-        <v>100</v>
       </c>
       <c r="O33" s="3">
         <v>100</v>
       </c>
       <c r="P33" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q33" s="3">
         <v>1500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-800</v>
       </c>
-      <c r="AD33" s="3">
-        <v>0</v>
-      </c>
       <c r="AE33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="3">
         <v>300</v>
       </c>
-      <c r="AF33" s="3">
-        <v>0</v>
-      </c>
       <c r="AG33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="3">
         <v>-300</v>
       </c>
-      <c r="AH33" s="3">
-        <v>0</v>
-      </c>
       <c r="AI33" s="3">
         <v>0</v>
       </c>
       <c r="AJ33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-900</v>
-      </c>
-      <c r="N35" s="3">
-        <v>100</v>
       </c>
       <c r="O35" s="3">
         <v>100</v>
       </c>
       <c r="P35" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q35" s="3">
         <v>1500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-800</v>
       </c>
-      <c r="AD35" s="3">
-        <v>0</v>
-      </c>
       <c r="AE35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="3">
         <v>300</v>
       </c>
-      <c r="AF35" s="3">
-        <v>0</v>
-      </c>
       <c r="AG35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="3">
         <v>-300</v>
       </c>
-      <c r="AH35" s="3">
-        <v>0</v>
-      </c>
       <c r="AI35" s="3">
         <v>0</v>
       </c>
       <c r="AJ35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E41" s="3">
         <v>1300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2900</v>
-      </c>
-      <c r="V41" s="3">
-        <v>900</v>
       </c>
       <c r="W41" s="3">
         <v>900</v>
       </c>
       <c r="X41" s="3">
+        <v>900</v>
+      </c>
+      <c r="Y41" s="3">
         <v>800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3907,201 +3996,207 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6600</v>
+        <v>6400</v>
       </c>
       <c r="E43" s="3">
         <v>6600</v>
       </c>
       <c r="F43" s="3">
+        <v>6600</v>
+      </c>
+      <c r="G43" s="3">
         <v>7800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>12900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>14300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>13000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>17100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>20000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>18100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>17500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>16900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>19100</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>16000</v>
       </c>
       <c r="AC43" s="3">
         <v>16000</v>
       </c>
       <c r="AD43" s="3">
+        <v>16000</v>
+      </c>
+      <c r="AE43" s="3">
         <v>16500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>14100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>14700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>12500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>11800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>11200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E44" s="3">
         <v>9900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>10000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>10600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>11000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>11900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>10500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8200</v>
-      </c>
-      <c r="N44" s="3">
-        <v>7800</v>
       </c>
       <c r="O44" s="3">
         <v>7800</v>
       </c>
       <c r="P44" s="3">
+        <v>7800</v>
+      </c>
+      <c r="Q44" s="3">
         <v>7900</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>6800</v>
       </c>
       <c r="R44" s="3">
         <v>6800</v>
       </c>
       <c r="S44" s="3">
+        <v>6800</v>
+      </c>
+      <c r="T44" s="3">
         <v>7200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>7100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>7300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>7100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>7000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>6700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5500</v>
-      </c>
-      <c r="AD44" s="3">
-        <v>5100</v>
       </c>
       <c r="AE44" s="3">
         <v>5100</v>
       </c>
       <c r="AF44" s="3">
-        <v>6100</v>
+        <v>5100</v>
       </c>
       <c r="AG44" s="3">
         <v>6100</v>
@@ -4110,13 +4205,16 @@
         <v>6100</v>
       </c>
       <c r="AI44" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>4800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4141,14 +4239,14 @@
       <c r="J45" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
-      </c>
-      <c r="M45" s="3">
-        <v>600</v>
       </c>
       <c r="N45" s="3">
         <v>600</v>
@@ -4160,19 +4258,19 @@
         <v>600</v>
       </c>
       <c r="Q45" s="3">
+        <v>600</v>
+      </c>
+      <c r="R45" s="3">
         <v>800</v>
-      </c>
-      <c r="R45" s="3">
-        <v>600</v>
       </c>
       <c r="S45" s="3">
         <v>600</v>
       </c>
       <c r="T45" s="3">
+        <v>600</v>
+      </c>
+      <c r="U45" s="3">
         <v>500</v>
-      </c>
-      <c r="U45" s="3">
-        <v>600</v>
       </c>
       <c r="V45" s="3">
         <v>600</v>
@@ -4190,158 +4288,164 @@
         <v>600</v>
       </c>
       <c r="AA45" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB45" s="3">
         <v>700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>800</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>900</v>
       </c>
       <c r="AD45" s="3">
         <v>900</v>
       </c>
       <c r="AE45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AF45" s="3">
         <v>800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E46" s="3">
         <v>18200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>20300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22000</v>
-      </c>
-      <c r="L46" s="3">
-        <v>23400</v>
       </c>
       <c r="M46" s="3">
         <v>23400</v>
       </c>
       <c r="N46" s="3">
+        <v>23400</v>
+      </c>
+      <c r="O46" s="3">
         <v>25600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>25000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>24700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>23200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>23300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>22200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>23600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>23800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>26100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>27900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>26600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>26200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>26800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>26400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>22900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>23400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>23700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>21700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>23600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>22700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>20600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>20100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E47" s="3">
-        <v>100</v>
+      <c r="E47" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="F47" s="3">
         <v>100</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" s="3">
+        <v>100</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="H47" s="3">
-        <v>100</v>
       </c>
       <c r="I47" s="3">
         <v>100</v>
@@ -4358,8 +4462,8 @@
       <c r="M47" s="3">
         <v>100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>19</v>
+      <c r="N47" s="3">
+        <v>100</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>19</v>
@@ -4376,8 +4480,8 @@
       <c r="S47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -4418,112 +4522,115 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>19</v>
+      <c r="AH47" s="3">
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AJ47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK47" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E48" s="3">
         <v>4000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>15500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>15700</v>
-      </c>
-      <c r="AH48" s="3">
-        <v>500</v>
       </c>
       <c r="AI48" s="3">
         <v>500</v>
@@ -4531,37 +4638,40 @@
       <c r="AJ48" s="3">
         <v>500</v>
       </c>
+      <c r="AK48" s="3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E49" s="3">
         <v>5200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5300</v>
-      </c>
-      <c r="F49" s="3">
-        <v>5200</v>
       </c>
       <c r="G49" s="3">
         <v>5200</v>
       </c>
       <c r="H49" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I49" s="3">
         <v>5400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5600</v>
-      </c>
-      <c r="J49" s="3">
-        <v>3400</v>
       </c>
       <c r="K49" s="3">
         <v>3400</v>
       </c>
       <c r="L49" s="3">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="M49" s="3">
         <v>3500</v>
@@ -4570,46 +4680,46 @@
         <v>3500</v>
       </c>
       <c r="O49" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="P49" s="3">
         <v>3600</v>
       </c>
       <c r="Q49" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="R49" s="3">
         <v>3700</v>
       </c>
       <c r="S49" s="3">
+        <v>3700</v>
+      </c>
+      <c r="T49" s="3">
         <v>3800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6700</v>
-      </c>
-      <c r="W49" s="3">
-        <v>6900</v>
       </c>
       <c r="X49" s="3">
         <v>6900</v>
       </c>
       <c r="Y49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Z49" s="3">
         <v>6800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>11900</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>16300</v>
       </c>
       <c r="AC49" s="3">
         <v>16300</v>
@@ -4621,13 +4731,13 @@
         <v>16300</v>
       </c>
       <c r="AF49" s="3">
+        <v>16300</v>
+      </c>
+      <c r="AG49" s="3">
         <v>2500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2100</v>
-      </c>
-      <c r="AH49" s="3">
-        <v>1100</v>
       </c>
       <c r="AI49" s="3">
         <v>1100</v>
@@ -4635,8 +4745,11 @@
       <c r="AJ49" s="3">
         <v>1100</v>
       </c>
+      <c r="AK49" s="3">
+        <v>1100</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,8 +4959,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4852,16 +4971,16 @@
         <v>200</v>
       </c>
       <c r="E52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
       </c>
       <c r="G52" s="3">
+        <v>100</v>
+      </c>
+      <c r="H52" s="3">
         <v>200</v>
-      </c>
-      <c r="H52" s="3">
-        <v>100</v>
       </c>
       <c r="I52" s="3">
         <v>100</v>
@@ -4879,13 +4998,13 @@
         <v>100</v>
       </c>
       <c r="N52" s="3">
+        <v>100</v>
+      </c>
+      <c r="O52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>100</v>
-      </c>
-      <c r="P52" s="3">
-        <v>200</v>
       </c>
       <c r="Q52" s="3">
         <v>200</v>
@@ -4903,22 +5022,22 @@
         <v>200</v>
       </c>
       <c r="V52" s="3">
+        <v>200</v>
+      </c>
+      <c r="W52" s="3">
         <v>300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>700</v>
-      </c>
-      <c r="X52" s="3">
-        <v>600</v>
       </c>
       <c r="Y52" s="3">
         <v>600</v>
       </c>
       <c r="Z52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA52" s="3">
         <v>300</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>400</v>
       </c>
       <c r="AB52" s="3">
         <v>400</v>
@@ -4927,28 +5046,31 @@
         <v>400</v>
       </c>
       <c r="AD52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AE52" s="3">
         <v>500</v>
       </c>
       <c r="AF52" s="3">
+        <v>500</v>
+      </c>
+      <c r="AG52" s="3">
         <v>15100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>15000</v>
-      </c>
-      <c r="AH52" s="3">
-        <v>2100</v>
       </c>
       <c r="AI52" s="3">
         <v>2100</v>
       </c>
       <c r="AJ52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AK52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E54" s="3">
         <v>27500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>28500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>29200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>28200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>28300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>30100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>30300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>31600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>30100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>35200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>35900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>38500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>41100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>40000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>39800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>40400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>49900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>50800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>51500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>52500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>50700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>56600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>55600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>24400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>23700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>23200</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,34 +5360,35 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E57" s="3">
         <v>4800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>4500</v>
       </c>
       <c r="H57" s="3">
         <v>4500</v>
       </c>
       <c r="I57" s="3">
-        <v>4200</v>
+        <v>4500</v>
       </c>
       <c r="J57" s="3">
         <v>4200</v>
       </c>
       <c r="K57" s="3">
-        <v>3300</v>
+        <v>4200</v>
       </c>
       <c r="L57" s="3">
         <v>3300</v>
@@ -5267,108 +5397,111 @@
         <v>3300</v>
       </c>
       <c r="N57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="O57" s="3">
         <v>4400</v>
-      </c>
-      <c r="O57" s="3">
-        <v>3500</v>
       </c>
       <c r="P57" s="3">
         <v>3500</v>
       </c>
       <c r="Q57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="R57" s="3">
         <v>2600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>7200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>6800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E58" s="3">
         <v>2000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1000</v>
       </c>
       <c r="F58" s="3">
         <v>1000</v>
       </c>
       <c r="G58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H58" s="3">
         <v>800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>600</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -5386,40 +5519,40 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>800</v>
-      </c>
-      <c r="T58" s="3">
-        <v>200</v>
       </c>
       <c r="U58" s="3">
         <v>200</v>
       </c>
       <c r="V58" s="3">
+        <v>200</v>
+      </c>
+      <c r="W58" s="3">
         <v>1500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>900</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
       <c r="Z58" s="3">
         <v>0</v>
       </c>
       <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
         <v>2000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2600</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>900</v>
       </c>
       <c r="AE58" s="3">
         <v>900</v>
@@ -5430,8 +5563,8 @@
       <c r="AG58" s="3">
         <v>900</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>19</v>
+      <c r="AH58" s="3">
+        <v>900</v>
       </c>
       <c r="AI58" s="3" t="s">
         <v>19</v>
@@ -5439,242 +5572,251 @@
       <c r="AJ58" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E59" s="3">
         <v>2300</v>
-      </c>
-      <c r="E59" s="3">
-        <v>3600</v>
       </c>
       <c r="F59" s="3">
         <v>3600</v>
       </c>
       <c r="G59" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H59" s="3">
         <v>2800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4400</v>
-      </c>
-      <c r="L59" s="3">
-        <v>4500</v>
       </c>
       <c r="M59" s="3">
         <v>4500</v>
       </c>
       <c r="N59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="O59" s="3">
         <v>4900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3900</v>
-      </c>
-      <c r="R59" s="3">
-        <v>3800</v>
       </c>
       <c r="S59" s="3">
         <v>3800</v>
       </c>
       <c r="T59" s="3">
-        <v>4500</v>
+        <v>3800</v>
       </c>
       <c r="U59" s="3">
         <v>4500</v>
       </c>
       <c r="V59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="W59" s="3">
         <v>5200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E60" s="3">
         <v>11800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>13400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11600</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>10600</v>
       </c>
       <c r="Z60" s="3">
         <v>10600</v>
       </c>
       <c r="AA60" s="3">
+        <v>10600</v>
+      </c>
+      <c r="AB60" s="3">
         <v>13200</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>11300</v>
       </c>
       <c r="AC60" s="3">
         <v>11300</v>
       </c>
       <c r="AD60" s="3">
+        <v>11300</v>
+      </c>
+      <c r="AE60" s="3">
         <v>11000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>9400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1800</v>
-      </c>
-      <c r="E61" s="3">
-        <v>1700</v>
       </c>
       <c r="F61" s="3">
         <v>1700</v>
       </c>
       <c r="G61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H61" s="3">
         <v>700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>400</v>
-      </c>
-      <c r="I61" s="3">
-        <v>500</v>
       </c>
       <c r="J61" s="3">
         <v>500</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -5692,22 +5834,22 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3">
         <v>1900</v>
       </c>
       <c r="S61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="T61" s="3">
         <v>1000</v>
-      </c>
-      <c r="T61" s="3">
-        <v>1700</v>
       </c>
       <c r="U61" s="3">
         <v>1700</v>
       </c>
       <c r="V61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="W61" s="3">
         <v>0</v>
@@ -5737,7 +5879,7 @@
         <v>0</v>
       </c>
       <c r="AF61" s="3">
-        <v>3100</v>
+        <v>0</v>
       </c>
       <c r="AG61" s="3">
         <v>3100</v>
@@ -5751,112 +5893,118 @@
       <c r="AJ61" s="3">
         <v>3100</v>
       </c>
+      <c r="AK61" s="3">
+        <v>3100</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3200</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>3500</v>
       </c>
       <c r="R62" s="3">
         <v>3500</v>
       </c>
       <c r="S62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="T62" s="3">
         <v>3000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>5200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>8300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>10700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>10800</v>
-      </c>
-      <c r="AH62" s="3">
-        <v>500</v>
       </c>
       <c r="AI62" s="3">
         <v>500</v>
       </c>
       <c r="AJ62" s="3">
+        <v>500</v>
+      </c>
+      <c r="AK62" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E66" s="3">
         <v>16300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>15100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>16300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>17800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>16200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>15900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>22100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>18700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>18800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>17400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>23800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>22900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>9200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,103 +6895,106 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-47600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-46500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-45500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-44000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-42900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-41000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-40600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-39800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-38300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-36900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-36600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-35700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-35800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-35900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-37400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-37800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-39500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-35500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-35200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-34600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-33400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-32900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-32300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-32000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-28700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-24300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-23700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-22900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-22800</v>
-      </c>
-      <c r="AF72" s="3">
-        <v>-23100</v>
       </c>
       <c r="AG72" s="3">
         <v>-23100</v>
       </c>
       <c r="AH72" s="3">
-        <v>-22800</v>
+        <v>-23100</v>
       </c>
       <c r="AI72" s="3">
         <v>-22800</v>
@@ -6829,8 +7002,11 @@
       <c r="AJ72" s="3">
         <v>-22800</v>
       </c>
+      <c r="AK72" s="3">
+        <v>-22800</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E76" s="3">
         <v>11300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>21300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>21500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>22100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>23300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>23700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>24200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>24600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>27800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>32100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>32600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>33300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>33200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>32900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>32700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-900</v>
-      </c>
-      <c r="N81" s="3">
-        <v>100</v>
       </c>
       <c r="O81" s="3">
         <v>100</v>
       </c>
       <c r="P81" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q81" s="3">
         <v>1500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-800</v>
       </c>
-      <c r="AD81" s="3">
-        <v>0</v>
-      </c>
       <c r="AE81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="3">
         <v>300</v>
       </c>
-      <c r="AF81" s="3">
-        <v>0</v>
-      </c>
       <c r="AG81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="3">
         <v>-300</v>
       </c>
-      <c r="AH81" s="3">
-        <v>0</v>
-      </c>
       <c r="AI81" s="3">
         <v>0</v>
       </c>
       <c r="AJ81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,16 +7797,17 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
         <v>200</v>
-      </c>
-      <c r="E83" s="3">
-        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -7672,7 +7870,7 @@
         <v>100</v>
       </c>
       <c r="Z83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA83" s="3">
         <v>200</v>
@@ -7696,7 +7894,7 @@
         <v>200</v>
       </c>
       <c r="AH83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AI83" s="3">
         <v>100</v>
@@ -7704,8 +7902,11 @@
       <c r="AJ83" s="3">
         <v>100</v>
       </c>
+      <c r="AK83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-200</v>
+        <v>4200</v>
       </c>
       <c r="E89" s="3">
         <v>-200</v>
       </c>
       <c r="F89" s="3">
-        <v>200</v>
+        <v>-200</v>
       </c>
       <c r="G89" s="3">
         <v>200</v>
       </c>
       <c r="H89" s="3">
+        <v>200</v>
+      </c>
+      <c r="I89" s="3">
         <v>-1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1900</v>
-      </c>
-      <c r="O89" s="3">
-        <v>300</v>
       </c>
       <c r="P89" s="3">
         <v>300</v>
       </c>
       <c r="Q89" s="3">
+        <v>300</v>
+      </c>
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,37 +8585,38 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="s">
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
@@ -8405,14 +8625,14 @@
         <v>-100</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -8426,11 +8646,11 @@
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
@@ -8441,22 +8661,22 @@
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-100</v>
       </c>
       <c r="AG91" s="3">
         <v>-100</v>
@@ -8468,10 +8688,13 @@
         <v>-100</v>
       </c>
       <c r="AJ91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,53 +8904,56 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3" t="s">
+      <c r="K94" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
@@ -8732,13 +8961,13 @@
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W94" s="3">
         <v>-100</v>
@@ -8747,43 +8976,46 @@
         <v>-100</v>
       </c>
       <c r="Y94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>5000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>500</v>
-      </c>
-      <c r="AH94" s="3">
-        <v>-100</v>
       </c>
       <c r="AI94" s="3">
         <v>-100</v>
       </c>
       <c r="AJ94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,8 +9079,8 @@
       <c r="J96" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,35 +9478,38 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>500</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
-      <c r="J100" s="3" t="s">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
@@ -9284,64 +9529,67 @@
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>1900</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>900</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1700</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
         <v>0</v>
       </c>
       <c r="AH100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI100" s="3">
         <v>100</v>
       </c>
       <c r="AJ100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK100" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,8 +9614,8 @@
       <c r="J101" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9444,108 +9692,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E102" s="3">
         <v>400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-2600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1900</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TGEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TGEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
   <si>
     <t>TGEN</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E8" s="3">
         <v>6100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5000</v>
-      </c>
-      <c r="R8" s="3">
-        <v>6100</v>
       </c>
       <c r="S8" s="3">
         <v>6100</v>
       </c>
       <c r="T8" s="3">
+        <v>6100</v>
+      </c>
+      <c r="U8" s="3">
         <v>5700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8000</v>
-      </c>
-      <c r="X8" s="3">
-        <v>8700</v>
       </c>
       <c r="Y8" s="3">
         <v>8700</v>
       </c>
       <c r="Z8" s="3">
+        <v>8700</v>
+      </c>
+      <c r="AA8" s="3">
         <v>7900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E9" s="3">
         <v>3300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2200</v>
-      </c>
-      <c r="M9" s="3">
-        <v>3700</v>
       </c>
       <c r="N9" s="3">
         <v>3700</v>
       </c>
       <c r="O9" s="3">
+        <v>3700</v>
+      </c>
+      <c r="P9" s="3">
         <v>4300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>6500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E10" s="3">
         <v>2700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,13 +1179,14 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E12" s="3">
         <v>200</v>
@@ -1181,10 +1195,10 @@
         <v>200</v>
       </c>
       <c r="G12" s="3">
+        <v>200</v>
+      </c>
+      <c r="H12" s="3">
         <v>300</v>
-      </c>
-      <c r="H12" s="3">
-        <v>200</v>
       </c>
       <c r="I12" s="3">
         <v>200</v>
@@ -1205,13 +1219,13 @@
         <v>200</v>
       </c>
       <c r="O12" s="3">
+        <v>200</v>
+      </c>
+      <c r="P12" s="3">
         <v>100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>200</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>100</v>
       </c>
       <c r="R12" s="3">
         <v>100</v>
@@ -1226,10 +1240,10 @@
         <v>100</v>
       </c>
       <c r="V12" s="3">
+        <v>100</v>
+      </c>
+      <c r="W12" s="3">
         <v>200</v>
-      </c>
-      <c r="W12" s="3">
-        <v>400</v>
       </c>
       <c r="X12" s="3">
         <v>400</v>
@@ -1241,7 +1255,7 @@
         <v>400</v>
       </c>
       <c r="AA12" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AB12" s="3">
         <v>300</v>
@@ -1250,16 +1264,16 @@
         <v>300</v>
       </c>
       <c r="AD12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE12" s="3">
         <v>400</v>
-      </c>
-      <c r="AE12" s="3">
-        <v>300</v>
       </c>
       <c r="AF12" s="3">
         <v>300</v>
       </c>
       <c r="AG12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AH12" s="3">
         <v>200</v>
@@ -1268,13 +1282,16 @@
         <v>200</v>
       </c>
       <c r="AJ12" s="3">
+        <v>200</v>
+      </c>
+      <c r="AK12" s="3">
         <v>100</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1380,17 +1397,20 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
@@ -1401,17 +1421,17 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1425,43 +1445,43 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-2400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-1900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2900</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>19</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB14" s="3">
         <v>3700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>4400</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>19</v>
@@ -1478,8 +1498,8 @@
       <c r="AH14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AI14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
@@ -1487,13 +1507,16 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -1508,17 +1531,17 @@
         <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>200</v>
       </c>
       <c r="K15" s="3">
+        <v>200</v>
+      </c>
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1594,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E17" s="3">
         <v>7000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7700</v>
-      </c>
-      <c r="I17" s="3">
-        <v>7500</v>
       </c>
       <c r="J17" s="3">
         <v>7500</v>
       </c>
       <c r="K17" s="3">
+        <v>7500</v>
+      </c>
+      <c r="L17" s="3">
         <v>6800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9100</v>
-      </c>
-      <c r="X17" s="3">
-        <v>9200</v>
       </c>
       <c r="Y17" s="3">
         <v>9200</v>
       </c>
       <c r="Z17" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AA17" s="3">
         <v>8200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>11500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>7100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-900</v>
+        <v>-600</v>
       </c>
       <c r="E18" s="3">
         <v>-900</v>
       </c>
       <c r="F18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G18" s="3">
         <v>-1500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-800</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-1400</v>
       </c>
       <c r="L18" s="3">
         <v>-1400</v>
       </c>
       <c r="M18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="N18" s="3">
         <v>-200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-800</v>
       </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
       <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
         <v>200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1100</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-500</v>
       </c>
       <c r="Y18" s="3">
         <v>-500</v>
       </c>
       <c r="Z18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-600</v>
       </c>
       <c r="AD18" s="3">
         <v>-600</v>
       </c>
       <c r="AE18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AF18" s="3">
         <v>100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-200</v>
       </c>
-      <c r="AI18" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ18" s="3">
         <v>0</v>
       </c>
       <c r="AK18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1883,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1922,26 +1956,26 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1958,20 +1992,20 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
@@ -1990,115 +2024,121 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-800</v>
+        <v>-400</v>
       </c>
       <c r="E21" s="3">
         <v>-800</v>
       </c>
       <c r="F21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="G21" s="3">
         <v>-1300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-600</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-1300</v>
       </c>
       <c r="L21" s="3">
         <v>-1300</v>
       </c>
       <c r="M21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="N21" s="3">
         <v>-100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-700</v>
-      </c>
-      <c r="O21" s="3">
-        <v>200</v>
       </c>
       <c r="P21" s="3">
         <v>200</v>
       </c>
       <c r="Q21" s="3">
+        <v>200</v>
+      </c>
+      <c r="R21" s="3">
         <v>1600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1000</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-400</v>
       </c>
       <c r="Y21" s="3">
         <v>-400</v>
       </c>
       <c r="Z21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-100</v>
-      </c>
-      <c r="AI21" s="3">
-        <v>100</v>
       </c>
       <c r="AJ21" s="3">
         <v>100</v>
       </c>
       <c r="AK21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2157,13 +2197,13 @@
         <v>0</v>
       </c>
       <c r="V22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W22" s="3">
         <v>100</v>
       </c>
       <c r="X22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -2175,11 +2215,11 @@
         <v>0</v>
       </c>
       <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
         <v>100</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
@@ -2204,139 +2244,145 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-800</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-1400</v>
       </c>
       <c r="L23" s="3">
         <v>-1400</v>
       </c>
       <c r="M23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="N23" s="3">
         <v>-200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-800</v>
-      </c>
-      <c r="O23" s="3">
-        <v>100</v>
       </c>
       <c r="P23" s="3">
         <v>100</v>
       </c>
       <c r="Q23" s="3">
+        <v>100</v>
+      </c>
+      <c r="R23" s="3">
         <v>1500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-700</v>
       </c>
-      <c r="AE23" s="3">
-        <v>0</v>
-      </c>
       <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="3">
         <v>300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-300</v>
       </c>
-      <c r="AI23" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ23" s="3">
         <v>0</v>
       </c>
       <c r="AK23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -2397,14 +2443,14 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-      <c r="AE24" s="3" t="s">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG24" s="3" t="s">
-        <v>19</v>
+      <c r="AG24" s="3">
+        <v>0</v>
       </c>
       <c r="AH24" s="3" t="s">
         <v>19</v>
@@ -2418,8 +2464,11 @@
       <c r="AK24" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="AL24" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-800</v>
-      </c>
-      <c r="O26" s="3">
-        <v>100</v>
       </c>
       <c r="P26" s="3">
         <v>100</v>
       </c>
       <c r="Q26" s="3">
+        <v>100</v>
+      </c>
+      <c r="R26" s="3">
         <v>1500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-700</v>
       </c>
-      <c r="AE26" s="3">
-        <v>0</v>
-      </c>
       <c r="AF26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="3">
         <v>300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-300</v>
       </c>
-      <c r="AI26" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ26" s="3">
         <v>0</v>
       </c>
       <c r="AK26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-900</v>
-      </c>
-      <c r="O27" s="3">
-        <v>100</v>
       </c>
       <c r="P27" s="3">
         <v>100</v>
       </c>
       <c r="Q27" s="3">
+        <v>100</v>
+      </c>
+      <c r="R27" s="3">
         <v>1500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-800</v>
       </c>
-      <c r="AE27" s="3">
-        <v>0</v>
-      </c>
       <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="3">
         <v>300</v>
       </c>
-      <c r="AG27" s="3">
-        <v>0</v>
-      </c>
       <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3">
         <v>-300</v>
       </c>
-      <c r="AI27" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ27" s="3">
         <v>0</v>
       </c>
       <c r="AK27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3206,26 +3276,26 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -3242,20 +3312,20 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
@@ -3274,115 +3344,121 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-900</v>
-      </c>
-      <c r="O33" s="3">
-        <v>100</v>
       </c>
       <c r="P33" s="3">
         <v>100</v>
       </c>
       <c r="Q33" s="3">
+        <v>100</v>
+      </c>
+      <c r="R33" s="3">
         <v>1500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-800</v>
       </c>
-      <c r="AE33" s="3">
-        <v>0</v>
-      </c>
       <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3">
         <v>300</v>
       </c>
-      <c r="AG33" s="3">
-        <v>0</v>
-      </c>
       <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3">
         <v>-300</v>
       </c>
-      <c r="AI33" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ33" s="3">
         <v>0</v>
       </c>
       <c r="AK33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-900</v>
-      </c>
-      <c r="O35" s="3">
-        <v>100</v>
       </c>
       <c r="P35" s="3">
         <v>100</v>
       </c>
       <c r="Q35" s="3">
+        <v>100</v>
+      </c>
+      <c r="R35" s="3">
         <v>1500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-800</v>
       </c>
-      <c r="AE35" s="3">
-        <v>0</v>
-      </c>
       <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="3">
         <v>300</v>
       </c>
-      <c r="AG35" s="3">
-        <v>0</v>
-      </c>
       <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="3">
         <v>-300</v>
       </c>
-      <c r="AI35" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ35" s="3">
         <v>0</v>
       </c>
       <c r="AK35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E41" s="3">
         <v>5400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2900</v>
-      </c>
-      <c r="W41" s="3">
-        <v>900</v>
       </c>
       <c r="X41" s="3">
         <v>900</v>
       </c>
       <c r="Y41" s="3">
+        <v>900</v>
+      </c>
+      <c r="Z41" s="3">
         <v>800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3999,207 +4089,213 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6400</v>
-      </c>
-      <c r="E43" s="3">
-        <v>6600</v>
       </c>
       <c r="F43" s="3">
         <v>6600</v>
       </c>
       <c r="G43" s="3">
+        <v>6600</v>
+      </c>
+      <c r="H43" s="3">
         <v>7800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>12200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>14300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>13000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>17100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>20000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>18100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>17500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>16900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>19100</v>
-      </c>
-      <c r="AC43" s="3">
-        <v>16000</v>
       </c>
       <c r="AD43" s="3">
         <v>16000</v>
       </c>
       <c r="AE43" s="3">
+        <v>16000</v>
+      </c>
+      <c r="AF43" s="3">
         <v>16500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>14100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>14700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>12500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>11800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>11200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E44" s="3">
         <v>9600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>10100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>10000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>10600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>11000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>11900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>10500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8200</v>
-      </c>
-      <c r="O44" s="3">
-        <v>7800</v>
       </c>
       <c r="P44" s="3">
         <v>7800</v>
       </c>
       <c r="Q44" s="3">
+        <v>7800</v>
+      </c>
+      <c r="R44" s="3">
         <v>7900</v>
-      </c>
-      <c r="R44" s="3">
-        <v>6800</v>
       </c>
       <c r="S44" s="3">
         <v>6800</v>
       </c>
       <c r="T44" s="3">
+        <v>6800</v>
+      </c>
+      <c r="U44" s="3">
         <v>7200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>7100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>7500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>7100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>7000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5500</v>
-      </c>
-      <c r="AE44" s="3">
-        <v>5100</v>
       </c>
       <c r="AF44" s="3">
         <v>5100</v>
       </c>
       <c r="AG44" s="3">
-        <v>6100</v>
+        <v>5100</v>
       </c>
       <c r="AH44" s="3">
         <v>6100</v>
@@ -4208,13 +4304,16 @@
         <v>6100</v>
       </c>
       <c r="AJ44" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AK44" s="3">
         <v>4800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4242,14 +4341,14 @@
       <c r="K45" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
-      </c>
-      <c r="N45" s="3">
-        <v>600</v>
       </c>
       <c r="O45" s="3">
         <v>600</v>
@@ -4261,19 +4360,19 @@
         <v>600</v>
       </c>
       <c r="R45" s="3">
+        <v>600</v>
+      </c>
+      <c r="S45" s="3">
         <v>800</v>
-      </c>
-      <c r="S45" s="3">
-        <v>600</v>
       </c>
       <c r="T45" s="3">
         <v>600</v>
       </c>
       <c r="U45" s="3">
+        <v>600</v>
+      </c>
+      <c r="V45" s="3">
         <v>500</v>
-      </c>
-      <c r="V45" s="3">
-        <v>600</v>
       </c>
       <c r="W45" s="3">
         <v>600</v>
@@ -4291,164 +4390,170 @@
         <v>600</v>
       </c>
       <c r="AB45" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC45" s="3">
         <v>700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>800</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>900</v>
       </c>
       <c r="AE45" s="3">
         <v>900</v>
       </c>
       <c r="AF45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AG45" s="3">
         <v>800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E46" s="3">
         <v>22100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>20300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22000</v>
-      </c>
-      <c r="M46" s="3">
-        <v>23400</v>
       </c>
       <c r="N46" s="3">
         <v>23400</v>
       </c>
       <c r="O46" s="3">
+        <v>23400</v>
+      </c>
+      <c r="P46" s="3">
         <v>25600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>25000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>24700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>23200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>23300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>22200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>23600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>23800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>26100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>27900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>26600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>26200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>26800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>26400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>22900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>23400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>23700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>21700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>23600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>22700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>20600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>20100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>19</v>
+      <c r="D47" s="3">
+        <v>100</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F47" s="3">
-        <v>100</v>
+      <c r="F47" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="G47" s="3">
         <v>100</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="H47" s="3">
+        <v>100</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="I47" s="3">
-        <v>100</v>
       </c>
       <c r="J47" s="3">
         <v>100</v>
@@ -4465,8 +4570,8 @@
       <c r="N47" s="3">
         <v>100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>19</v>
+      <c r="O47" s="3">
+        <v>100</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>19</v>
@@ -4483,8 +4588,8 @@
       <c r="T47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -4525,115 +4630,118 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-      <c r="AI47" s="3" t="s">
-        <v>19</v>
+      <c r="AI47" s="3">
+        <v>0</v>
       </c>
       <c r="AJ47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AK47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL47" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E48" s="3">
         <v>3900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>15500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>15700</v>
-      </c>
-      <c r="AI48" s="3">
-        <v>500</v>
       </c>
       <c r="AJ48" s="3">
         <v>500</v>
@@ -4641,40 +4749,43 @@
       <c r="AK48" s="3">
         <v>500</v>
       </c>
+      <c r="AL48" s="3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E49" s="3">
         <v>4900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5300</v>
-      </c>
-      <c r="G49" s="3">
-        <v>5200</v>
       </c>
       <c r="H49" s="3">
         <v>5200</v>
       </c>
       <c r="I49" s="3">
+        <v>5200</v>
+      </c>
+      <c r="J49" s="3">
         <v>5400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5600</v>
-      </c>
-      <c r="K49" s="3">
-        <v>3400</v>
       </c>
       <c r="L49" s="3">
         <v>3400</v>
       </c>
       <c r="M49" s="3">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="N49" s="3">
         <v>3500</v>
@@ -4683,46 +4794,46 @@
         <v>3500</v>
       </c>
       <c r="P49" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="Q49" s="3">
         <v>3600</v>
       </c>
       <c r="R49" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="S49" s="3">
         <v>3700</v>
       </c>
       <c r="T49" s="3">
+        <v>3700</v>
+      </c>
+      <c r="U49" s="3">
         <v>3800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6700</v>
-      </c>
-      <c r="X49" s="3">
-        <v>6900</v>
       </c>
       <c r="Y49" s="3">
         <v>6900</v>
       </c>
       <c r="Z49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="AA49" s="3">
         <v>6800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>11900</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>16300</v>
       </c>
       <c r="AD49" s="3">
         <v>16300</v>
@@ -4734,13 +4845,13 @@
         <v>16300</v>
       </c>
       <c r="AG49" s="3">
+        <v>16300</v>
+      </c>
+      <c r="AH49" s="3">
         <v>2500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2100</v>
-      </c>
-      <c r="AI49" s="3">
-        <v>1100</v>
       </c>
       <c r="AJ49" s="3">
         <v>1100</v>
@@ -4748,8 +4859,11 @@
       <c r="AK49" s="3">
         <v>1100</v>
       </c>
+      <c r="AL49" s="3">
+        <v>1100</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,28 +5079,31 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>200</v>
       </c>
       <c r="F52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G52" s="3">
         <v>100</v>
       </c>
       <c r="H52" s="3">
+        <v>100</v>
+      </c>
+      <c r="I52" s="3">
         <v>200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>100</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
@@ -5001,13 +5121,13 @@
         <v>100</v>
       </c>
       <c r="O52" s="3">
+        <v>100</v>
+      </c>
+      <c r="P52" s="3">
         <v>200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>100</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>200</v>
       </c>
       <c r="R52" s="3">
         <v>200</v>
@@ -5025,22 +5145,22 @@
         <v>200</v>
       </c>
       <c r="W52" s="3">
+        <v>200</v>
+      </c>
+      <c r="X52" s="3">
         <v>300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>700</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>600</v>
       </c>
       <c r="Z52" s="3">
         <v>600</v>
       </c>
       <c r="AA52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB52" s="3">
         <v>300</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>400</v>
       </c>
       <c r="AC52" s="3">
         <v>400</v>
@@ -5049,28 +5169,31 @@
         <v>400</v>
       </c>
       <c r="AE52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AF52" s="3">
         <v>500</v>
       </c>
       <c r="AG52" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH52" s="3">
         <v>15100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>15000</v>
-      </c>
-      <c r="AI52" s="3">
-        <v>2100</v>
       </c>
       <c r="AJ52" s="3">
         <v>2100</v>
       </c>
       <c r="AK52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AL52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>29700</v>
+      </c>
+      <c r="E54" s="3">
         <v>31100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>28500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>29800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>28200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>28300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>30100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>30300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>32500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>31300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>31600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>30100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>35200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>35900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>38500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>41100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>40000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>39800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>40400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>49900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>50800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>51500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>52500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>50700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>56600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>55600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>24400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>23700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>23200</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,37 +5491,38 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E57" s="3">
         <v>4100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>4500</v>
       </c>
       <c r="I57" s="3">
         <v>4500</v>
       </c>
       <c r="J57" s="3">
-        <v>4200</v>
+        <v>4500</v>
       </c>
       <c r="K57" s="3">
         <v>4200</v>
       </c>
       <c r="L57" s="3">
-        <v>3300</v>
+        <v>4200</v>
       </c>
       <c r="M57" s="3">
         <v>3300</v>
@@ -5400,111 +5531,114 @@
         <v>3300</v>
       </c>
       <c r="O57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="P57" s="3">
         <v>4400</v>
-      </c>
-      <c r="P57" s="3">
-        <v>3500</v>
       </c>
       <c r="Q57" s="3">
         <v>3500</v>
       </c>
       <c r="R57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="S57" s="3">
         <v>2600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>7200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>6800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E58" s="3">
         <v>2100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1000</v>
       </c>
       <c r="G58" s="3">
         <v>1000</v>
       </c>
       <c r="H58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>600</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -5522,40 +5656,40 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>800</v>
-      </c>
-      <c r="U58" s="3">
-        <v>200</v>
       </c>
       <c r="V58" s="3">
         <v>200</v>
       </c>
       <c r="W58" s="3">
+        <v>200</v>
+      </c>
+      <c r="X58" s="3">
         <v>1500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>900</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
       <c r="AA58" s="3">
         <v>0</v>
       </c>
       <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
         <v>2000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2600</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>900</v>
       </c>
       <c r="AF58" s="3">
         <v>900</v>
@@ -5566,8 +5700,8 @@
       <c r="AH58" s="3">
         <v>900</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>19</v>
+      <c r="AI58" s="3">
+        <v>900</v>
       </c>
       <c r="AJ58" s="3" t="s">
         <v>19</v>
@@ -5575,251 +5709,260 @@
       <c r="AK58" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E59" s="3">
         <v>7800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>3600</v>
       </c>
       <c r="G59" s="3">
         <v>3600</v>
       </c>
       <c r="H59" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I59" s="3">
         <v>2800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>4500</v>
       </c>
       <c r="N59" s="3">
         <v>4500</v>
       </c>
       <c r="O59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="P59" s="3">
         <v>4900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3900</v>
-      </c>
-      <c r="S59" s="3">
-        <v>3800</v>
       </c>
       <c r="T59" s="3">
         <v>3800</v>
       </c>
       <c r="U59" s="3">
-        <v>4500</v>
+        <v>3800</v>
       </c>
       <c r="V59" s="3">
         <v>4500</v>
       </c>
       <c r="W59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="X59" s="3">
         <v>5200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E60" s="3">
         <v>16800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>13400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11600</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>10600</v>
       </c>
       <c r="AA60" s="3">
         <v>10600</v>
       </c>
       <c r="AB60" s="3">
+        <v>10600</v>
+      </c>
+      <c r="AC60" s="3">
         <v>13200</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>11300</v>
       </c>
       <c r="AD60" s="3">
         <v>11300</v>
       </c>
       <c r="AE60" s="3">
+        <v>11300</v>
+      </c>
+      <c r="AF60" s="3">
         <v>11000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>9400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1800</v>
-      </c>
-      <c r="F61" s="3">
-        <v>1700</v>
       </c>
       <c r="G61" s="3">
         <v>1700</v>
       </c>
       <c r="H61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I61" s="3">
         <v>700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>400</v>
-      </c>
-      <c r="J61" s="3">
-        <v>500</v>
       </c>
       <c r="K61" s="3">
         <v>500</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -5837,22 +5980,22 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="S61" s="3">
         <v>1900</v>
       </c>
       <c r="T61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="U61" s="3">
         <v>1000</v>
-      </c>
-      <c r="U61" s="3">
-        <v>1700</v>
       </c>
       <c r="V61" s="3">
         <v>1700</v>
       </c>
       <c r="W61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="X61" s="3">
         <v>0</v>
@@ -5882,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="AG61" s="3">
-        <v>3100</v>
+        <v>0</v>
       </c>
       <c r="AH61" s="3">
         <v>3100</v>
@@ -5896,115 +6039,121 @@
       <c r="AK61" s="3">
         <v>3100</v>
       </c>
+      <c r="AL61" s="3">
+        <v>3100</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E62" s="3">
         <v>1300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3200</v>
-      </c>
-      <c r="R62" s="3">
-        <v>3500</v>
       </c>
       <c r="S62" s="3">
         <v>3500</v>
       </c>
       <c r="T62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="U62" s="3">
         <v>3000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>5200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>8300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>10700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>10800</v>
-      </c>
-      <c r="AI62" s="3">
-        <v>500</v>
       </c>
       <c r="AJ62" s="3">
         <v>500</v>
       </c>
       <c r="AK62" s="3">
+        <v>500</v>
+      </c>
+      <c r="AL62" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E66" s="3">
         <v>21000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>15100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>17800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>15500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>22100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>18700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>18800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>17400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>23800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>22900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>9700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>9200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,106 +7069,109 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-47600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-46500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-45500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-44000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-42900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-41000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-40600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-39800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-38300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-36900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-36600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-35700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-35800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-35900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-37400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-37800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-39500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-35500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-35200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-34600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-33400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-32900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-32300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-32000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-28700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-24300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-23700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-22900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-22800</v>
-      </c>
-      <c r="AG72" s="3">
-        <v>-23100</v>
       </c>
       <c r="AH72" s="3">
         <v>-23100</v>
       </c>
       <c r="AI72" s="3">
-        <v>-22800</v>
+        <v>-23100</v>
       </c>
       <c r="AJ72" s="3">
         <v>-22800</v>
@@ -7005,8 +7179,11 @@
       <c r="AK72" s="3">
         <v>-22800</v>
       </c>
+      <c r="AL72" s="3">
+        <v>-22800</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E76" s="3">
         <v>10200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>21300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>22100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>23300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>23700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>24200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>24600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>27800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>32100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>32600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>33300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>33200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>32900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>32700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>14500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-900</v>
-      </c>
-      <c r="O81" s="3">
-        <v>100</v>
       </c>
       <c r="P81" s="3">
         <v>100</v>
       </c>
       <c r="Q81" s="3">
+        <v>100</v>
+      </c>
+      <c r="R81" s="3">
         <v>1500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-800</v>
       </c>
-      <c r="AE81" s="3">
-        <v>0</v>
-      </c>
       <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="3">
         <v>300</v>
       </c>
-      <c r="AG81" s="3">
-        <v>0</v>
-      </c>
       <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="3">
         <v>-300</v>
       </c>
-      <c r="AI81" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ81" s="3">
         <v>0</v>
       </c>
       <c r="AK81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,8 +7996,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7807,10 +8006,10 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
-      </c>
-      <c r="F83" s="3">
-        <v>100</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -7873,7 +8072,7 @@
         <v>100</v>
       </c>
       <c r="AA83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB83" s="3">
         <v>200</v>
@@ -7897,7 +8096,7 @@
         <v>200</v>
       </c>
       <c r="AI83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AJ83" s="3">
         <v>100</v>
@@ -7905,8 +8104,11 @@
       <c r="AK83" s="3">
         <v>100</v>
       </c>
+      <c r="AL83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E89" s="3">
         <v>4200</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-200</v>
       </c>
       <c r="F89" s="3">
         <v>-200</v>
       </c>
       <c r="G89" s="3">
-        <v>200</v>
+        <v>-200</v>
       </c>
       <c r="H89" s="3">
         <v>200</v>
       </c>
       <c r="I89" s="3">
+        <v>200</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1900</v>
-      </c>
-      <c r="P89" s="3">
-        <v>300</v>
       </c>
       <c r="Q89" s="3">
         <v>300</v>
       </c>
       <c r="R89" s="3">
+        <v>300</v>
+      </c>
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,8 +8806,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8595,31 +8816,31 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
-      <c r="K91" s="3" t="s">
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
@@ -8628,14 +8849,14 @@
         <v>-100</v>
       </c>
       <c r="P91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -8649,11 +8870,11 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
@@ -8664,22 +8885,22 @@
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>-100</v>
       </c>
       <c r="AH91" s="3">
         <v>-100</v>
@@ -8691,10 +8912,13 @@
         <v>-100</v>
       </c>
       <c r="AK91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,8 +9134,11 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8916,47 +9146,47 @@
         <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3" t="s">
+      <c r="L94" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
@@ -8964,13 +9194,13 @@
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X94" s="3">
         <v>-100</v>
@@ -8979,43 +9209,46 @@
         <v>-100</v>
       </c>
       <c r="Z94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>5000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>1400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>1300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>500</v>
-      </c>
-      <c r="AI94" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ94" s="3">
         <v>-100</v>
       </c>
       <c r="AK94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9082,8 +9316,8 @@
       <c r="K96" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,38 +9724,41 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>500</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
-      <c r="K100" s="3" t="s">
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
@@ -9532,64 +9778,67 @@
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>1900</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>900</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1700</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
       <c r="AH100" s="3">
         <v>0</v>
       </c>
       <c r="AI100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ100" s="3">
         <v>100</v>
       </c>
       <c r="AK100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL100" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9617,8 +9866,8 @@
       <c r="K101" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9695,111 +9944,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E102" s="3">
         <v>4100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-2600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1900</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TGEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TGEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>TGEN</t>
   </si>
@@ -656,162 +656,166 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -819,329 +823,338 @@
         <v>7300</v>
       </c>
       <c r="E8" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F8" s="3">
         <v>6100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5000</v>
-      </c>
-      <c r="S8" s="3">
-        <v>6100</v>
       </c>
       <c r="T8" s="3">
         <v>6100</v>
       </c>
       <c r="U8" s="3">
+        <v>6100</v>
+      </c>
+      <c r="V8" s="3">
         <v>5700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8000</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>8700</v>
       </c>
       <c r="Z8" s="3">
         <v>8700</v>
       </c>
       <c r="AA8" s="3">
+        <v>8700</v>
+      </c>
+      <c r="AB8" s="3">
         <v>7900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>9300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>8500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E9" s="3">
         <v>4100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2200</v>
-      </c>
-      <c r="N9" s="3">
-        <v>3700</v>
       </c>
       <c r="O9" s="3">
         <v>3700</v>
       </c>
       <c r="P9" s="3">
+        <v>3700</v>
+      </c>
+      <c r="Q9" s="3">
         <v>4300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>6300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>6500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E10" s="3">
         <v>3200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1189,7 +1203,7 @@
         <v>300</v>
       </c>
       <c r="E12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F12" s="3">
         <v>200</v>
@@ -1198,10 +1212,10 @@
         <v>200</v>
       </c>
       <c r="H12" s="3">
+        <v>200</v>
+      </c>
+      <c r="I12" s="3">
         <v>300</v>
-      </c>
-      <c r="I12" s="3">
-        <v>200</v>
       </c>
       <c r="J12" s="3">
         <v>200</v>
@@ -1222,13 +1236,13 @@
         <v>200</v>
       </c>
       <c r="P12" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>200</v>
-      </c>
-      <c r="R12" s="3">
-        <v>100</v>
       </c>
       <c r="S12" s="3">
         <v>100</v>
@@ -1243,10 +1257,10 @@
         <v>100</v>
       </c>
       <c r="W12" s="3">
+        <v>100</v>
+      </c>
+      <c r="X12" s="3">
         <v>200</v>
-      </c>
-      <c r="X12" s="3">
-        <v>400</v>
       </c>
       <c r="Y12" s="3">
         <v>400</v>
@@ -1258,7 +1272,7 @@
         <v>400</v>
       </c>
       <c r="AB12" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AC12" s="3">
         <v>300</v>
@@ -1267,16 +1281,16 @@
         <v>300</v>
       </c>
       <c r="AE12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF12" s="3">
         <v>400</v>
-      </c>
-      <c r="AF12" s="3">
-        <v>300</v>
       </c>
       <c r="AG12" s="3">
         <v>300</v>
       </c>
       <c r="AH12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AI12" s="3">
         <v>200</v>
@@ -1285,13 +1299,16 @@
         <v>200</v>
       </c>
       <c r="AK12" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL12" s="3">
         <v>100</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1409,11 +1429,11 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
@@ -1424,17 +1444,17 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1448,43 +1468,43 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-2400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-1900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2900</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>19</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC14" s="3">
         <v>3700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>4400</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>19</v>
@@ -1501,8 +1521,8 @@
       <c r="AI14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
+      <c r="AJ14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AK14" s="3">
         <v>0</v>
@@ -1510,8 +1530,11 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1519,7 +1542,7 @@
         <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1534,17 +1557,17 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>200</v>
       </c>
       <c r="L15" s="3">
+        <v>200</v>
+      </c>
+      <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E17" s="3">
         <v>7900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7700</v>
-      </c>
-      <c r="J17" s="3">
-        <v>7500</v>
       </c>
       <c r="K17" s="3">
         <v>7500</v>
       </c>
       <c r="L17" s="3">
+        <v>7500</v>
+      </c>
+      <c r="M17" s="3">
         <v>6800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9100</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>9200</v>
       </c>
       <c r="Z17" s="3">
         <v>9200</v>
       </c>
       <c r="AA17" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AB17" s="3">
         <v>8200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>11500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>10000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>7800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>6800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>7100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-600</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-900</v>
       </c>
       <c r="F18" s="3">
         <v>-900</v>
       </c>
       <c r="G18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H18" s="3">
         <v>-1500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-800</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-1400</v>
       </c>
       <c r="M18" s="3">
         <v>-1400</v>
       </c>
       <c r="N18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="O18" s="3">
         <v>-200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-800</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
       <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3">
         <v>200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-4100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1100</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-500</v>
       </c>
       <c r="Z18" s="3">
         <v>-500</v>
       </c>
       <c r="AA18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>-600</v>
       </c>
       <c r="AE18" s="3">
         <v>-600</v>
       </c>
       <c r="AF18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AG18" s="3">
         <v>100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ18" s="3">
-        <v>0</v>
-      </c>
       <c r="AK18" s="3">
         <v>0</v>
       </c>
       <c r="AL18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1917,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1959,26 +1993,26 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1995,20 +2029,20 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-100</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
@@ -2027,118 +2061,124 @@
       <c r="AL20" s="3">
         <v>0</v>
       </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-400</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-800</v>
       </c>
       <c r="F21" s="3">
         <v>-800</v>
       </c>
       <c r="G21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H21" s="3">
         <v>-1300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-600</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-1300</v>
       </c>
       <c r="M21" s="3">
         <v>-1300</v>
       </c>
       <c r="N21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="O21" s="3">
         <v>-100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-700</v>
-      </c>
-      <c r="P21" s="3">
-        <v>200</v>
       </c>
       <c r="Q21" s="3">
         <v>200</v>
       </c>
       <c r="R21" s="3">
+        <v>200</v>
+      </c>
+      <c r="S21" s="3">
         <v>1600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1000</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-400</v>
       </c>
       <c r="Z21" s="3">
         <v>-400</v>
       </c>
       <c r="AA21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-100</v>
-      </c>
-      <c r="AJ21" s="3">
-        <v>100</v>
       </c>
       <c r="AK21" s="3">
         <v>100</v>
       </c>
       <c r="AL21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2200,13 +2240,13 @@
         <v>0</v>
       </c>
       <c r="W22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X22" s="3">
         <v>100</v>
       </c>
       <c r="Y22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -2218,11 +2258,11 @@
         <v>0</v>
       </c>
       <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
         <v>100</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
       <c r="AE22" s="3">
         <v>0</v>
       </c>
@@ -2247,118 +2287,124 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-800</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-1400</v>
       </c>
       <c r="M23" s="3">
         <v>-1400</v>
       </c>
       <c r="N23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="O23" s="3">
         <v>-200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-800</v>
-      </c>
-      <c r="P23" s="3">
-        <v>100</v>
       </c>
       <c r="Q23" s="3">
         <v>100</v>
       </c>
       <c r="R23" s="3">
+        <v>100</v>
+      </c>
+      <c r="S23" s="3">
         <v>1500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-700</v>
       </c>
-      <c r="AF23" s="3">
-        <v>0</v>
-      </c>
       <c r="AG23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="3">
         <v>300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ23" s="3">
-        <v>0</v>
-      </c>
       <c r="AK23" s="3">
         <v>0</v>
       </c>
       <c r="AL23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -2368,24 +2414,24 @@
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -2446,14 +2492,14 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-      <c r="AF24" s="3" t="s">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="3" t="s">
-        <v>19</v>
+      <c r="AH24" s="3">
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="s">
         <v>19</v>
@@ -2467,8 +2513,11 @@
       <c r="AL24" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="AM24" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-800</v>
-      </c>
-      <c r="P26" s="3">
-        <v>100</v>
       </c>
       <c r="Q26" s="3">
         <v>100</v>
       </c>
       <c r="R26" s="3">
+        <v>100</v>
+      </c>
+      <c r="S26" s="3">
         <v>1500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-700</v>
       </c>
-      <c r="AF26" s="3">
-        <v>0</v>
-      </c>
       <c r="AG26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="3">
         <v>300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ26" s="3">
-        <v>0</v>
-      </c>
       <c r="AK26" s="3">
         <v>0</v>
       </c>
       <c r="AL26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-900</v>
-      </c>
-      <c r="P27" s="3">
-        <v>100</v>
       </c>
       <c r="Q27" s="3">
         <v>100</v>
       </c>
       <c r="R27" s="3">
+        <v>100</v>
+      </c>
+      <c r="S27" s="3">
         <v>1500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-800</v>
       </c>
-      <c r="AF27" s="3">
-        <v>0</v>
-      </c>
       <c r="AG27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="3">
         <v>300</v>
       </c>
-      <c r="AH27" s="3">
-        <v>0</v>
-      </c>
       <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ27" s="3">
-        <v>0</v>
-      </c>
       <c r="AK27" s="3">
         <v>0</v>
       </c>
       <c r="AL27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3279,26 +3349,26 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -3315,20 +3385,20 @@
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>100</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
@@ -3347,118 +3417,124 @@
       <c r="AL32" s="3">
         <v>0</v>
       </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-900</v>
-      </c>
-      <c r="P33" s="3">
-        <v>100</v>
       </c>
       <c r="Q33" s="3">
         <v>100</v>
       </c>
       <c r="R33" s="3">
+        <v>100</v>
+      </c>
+      <c r="S33" s="3">
         <v>1500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-800</v>
       </c>
-      <c r="AF33" s="3">
-        <v>0</v>
-      </c>
       <c r="AG33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="3">
         <v>300</v>
       </c>
-      <c r="AH33" s="3">
-        <v>0</v>
-      </c>
       <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ33" s="3">
-        <v>0</v>
-      </c>
       <c r="AK33" s="3">
         <v>0</v>
       </c>
       <c r="AL33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-900</v>
-      </c>
-      <c r="P35" s="3">
-        <v>100</v>
       </c>
       <c r="Q35" s="3">
         <v>100</v>
       </c>
       <c r="R35" s="3">
+        <v>100</v>
+      </c>
+      <c r="S35" s="3">
         <v>1500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-800</v>
       </c>
-      <c r="AF35" s="3">
-        <v>0</v>
-      </c>
       <c r="AG35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="3">
         <v>300</v>
       </c>
-      <c r="AH35" s="3">
-        <v>0</v>
-      </c>
       <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ35" s="3">
-        <v>0</v>
-      </c>
       <c r="AK35" s="3">
         <v>0</v>
       </c>
       <c r="AL35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E41" s="3">
         <v>4100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2900</v>
-      </c>
-      <c r="X41" s="3">
-        <v>900</v>
       </c>
       <c r="Y41" s="3">
         <v>900</v>
       </c>
       <c r="Z41" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA41" s="3">
         <v>800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4092,213 +4182,219 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E43" s="3">
         <v>6000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6400</v>
-      </c>
-      <c r="F43" s="3">
-        <v>6600</v>
       </c>
       <c r="G43" s="3">
         <v>6600</v>
       </c>
       <c r="H43" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I43" s="3">
         <v>7800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>12400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>14300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>13000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>17100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>20000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>18100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>17500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>16900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>19100</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>16000</v>
       </c>
       <c r="AE43" s="3">
         <v>16000</v>
       </c>
       <c r="AF43" s="3">
+        <v>16000</v>
+      </c>
+      <c r="AG43" s="3">
         <v>16500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>14100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>14700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>12500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>11800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>11200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E44" s="3">
         <v>9900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>10100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>10000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>10600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>11000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>11900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>10500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8200</v>
-      </c>
-      <c r="P44" s="3">
-        <v>7800</v>
       </c>
       <c r="Q44" s="3">
         <v>7800</v>
       </c>
       <c r="R44" s="3">
+        <v>7800</v>
+      </c>
+      <c r="S44" s="3">
         <v>7900</v>
-      </c>
-      <c r="S44" s="3">
-        <v>6800</v>
       </c>
       <c r="T44" s="3">
         <v>6800</v>
       </c>
       <c r="U44" s="3">
+        <v>6800</v>
+      </c>
+      <c r="V44" s="3">
         <v>7200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>7300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>7500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>6400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>7100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>7000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>6000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5500</v>
-      </c>
-      <c r="AF44" s="3">
-        <v>5100</v>
       </c>
       <c r="AG44" s="3">
         <v>5100</v>
       </c>
       <c r="AH44" s="3">
-        <v>6100</v>
+        <v>5100</v>
       </c>
       <c r="AI44" s="3">
         <v>6100</v>
@@ -4307,13 +4403,16 @@
         <v>6100</v>
       </c>
       <c r="AK44" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AL44" s="3">
         <v>4800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4344,14 +4443,14 @@
       <c r="L45" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
-      </c>
-      <c r="O45" s="3">
-        <v>600</v>
       </c>
       <c r="P45" s="3">
         <v>600</v>
@@ -4363,19 +4462,19 @@
         <v>600</v>
       </c>
       <c r="S45" s="3">
+        <v>600</v>
+      </c>
+      <c r="T45" s="3">
         <v>800</v>
-      </c>
-      <c r="T45" s="3">
-        <v>600</v>
       </c>
       <c r="U45" s="3">
         <v>600</v>
       </c>
       <c r="V45" s="3">
+        <v>600</v>
+      </c>
+      <c r="W45" s="3">
         <v>500</v>
-      </c>
-      <c r="W45" s="3">
-        <v>600</v>
       </c>
       <c r="X45" s="3">
         <v>600</v>
@@ -4393,170 +4492,176 @@
         <v>600</v>
       </c>
       <c r="AC45" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD45" s="3">
         <v>700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>800</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>900</v>
       </c>
       <c r="AF45" s="3">
         <v>900</v>
       </c>
       <c r="AG45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AH45" s="3">
         <v>800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E46" s="3">
         <v>20600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>20300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>22000</v>
-      </c>
-      <c r="N46" s="3">
-        <v>23400</v>
       </c>
       <c r="O46" s="3">
         <v>23400</v>
       </c>
       <c r="P46" s="3">
+        <v>23400</v>
+      </c>
+      <c r="Q46" s="3">
         <v>25600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>25000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>24700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>23200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>23300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>22200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>23600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>23800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>26100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>27900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>26600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>26200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>26800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>26400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>22900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>23400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>23700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>21700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>23600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>22700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>20600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>20100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
         <v>100</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>19</v>
+      <c r="E47" s="3">
+        <v>100</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G47" s="3">
-        <v>100</v>
+      <c r="G47" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="H47" s="3">
         <v>100</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="I47" s="3">
+        <v>100</v>
+      </c>
+      <c r="J47" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="J47" s="3">
-        <v>100</v>
       </c>
       <c r="K47" s="3">
         <v>100</v>
@@ -4573,8 +4678,8 @@
       <c r="O47" s="3">
         <v>100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>19</v>
+      <c r="P47" s="3">
+        <v>100</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>19</v>
@@ -4591,8 +4696,8 @@
       <c r="U47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -4633,118 +4738,121 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
-      <c r="AJ47" s="3" t="s">
-        <v>19</v>
+      <c r="AJ47" s="3">
+        <v>0</v>
       </c>
       <c r="AK47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AL47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM47" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E48" s="3">
         <v>4200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>11400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>15500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>15700</v>
-      </c>
-      <c r="AJ48" s="3">
-        <v>500</v>
       </c>
       <c r="AK48" s="3">
         <v>500</v>
@@ -4752,43 +4860,46 @@
       <c r="AL48" s="3">
         <v>500</v>
       </c>
+      <c r="AM48" s="3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E49" s="3">
         <v>4800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5300</v>
-      </c>
-      <c r="H49" s="3">
-        <v>5200</v>
       </c>
       <c r="I49" s="3">
         <v>5200</v>
       </c>
       <c r="J49" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K49" s="3">
         <v>5400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5600</v>
-      </c>
-      <c r="L49" s="3">
-        <v>3400</v>
       </c>
       <c r="M49" s="3">
         <v>3400</v>
       </c>
       <c r="N49" s="3">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="O49" s="3">
         <v>3500</v>
@@ -4797,46 +4908,46 @@
         <v>3500</v>
       </c>
       <c r="Q49" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="R49" s="3">
         <v>3600</v>
       </c>
       <c r="S49" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="T49" s="3">
         <v>3700</v>
       </c>
       <c r="U49" s="3">
+        <v>3700</v>
+      </c>
+      <c r="V49" s="3">
         <v>3800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6700</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>6900</v>
       </c>
       <c r="Z49" s="3">
         <v>6900</v>
       </c>
       <c r="AA49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="AB49" s="3">
         <v>6800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>6900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>11900</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>16300</v>
       </c>
       <c r="AE49" s="3">
         <v>16300</v>
@@ -4848,13 +4959,13 @@
         <v>16300</v>
       </c>
       <c r="AH49" s="3">
+        <v>16300</v>
+      </c>
+      <c r="AI49" s="3">
         <v>2500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2100</v>
-      </c>
-      <c r="AJ49" s="3">
-        <v>1100</v>
       </c>
       <c r="AK49" s="3">
         <v>1100</v>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3">
         <v>1100</v>
       </c>
+      <c r="AM49" s="3">
+        <v>1100</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,8 +5199,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5091,22 +5211,22 @@
         <v>100</v>
       </c>
       <c r="E52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3">
         <v>200</v>
       </c>
       <c r="G52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
       </c>
       <c r="I52" s="3">
+        <v>100</v>
+      </c>
+      <c r="J52" s="3">
         <v>200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>100</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
@@ -5124,13 +5244,13 @@
         <v>100</v>
       </c>
       <c r="P52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q52" s="3">
         <v>200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>100</v>
-      </c>
-      <c r="R52" s="3">
-        <v>200</v>
       </c>
       <c r="S52" s="3">
         <v>200</v>
@@ -5148,22 +5268,22 @@
         <v>200</v>
       </c>
       <c r="X52" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y52" s="3">
         <v>300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>700</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>600</v>
       </c>
       <c r="AA52" s="3">
         <v>600</v>
       </c>
       <c r="AB52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC52" s="3">
         <v>300</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>400</v>
       </c>
       <c r="AD52" s="3">
         <v>400</v>
@@ -5172,28 +5292,31 @@
         <v>400</v>
       </c>
       <c r="AF52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AG52" s="3">
         <v>500</v>
       </c>
       <c r="AH52" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI52" s="3">
         <v>15100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>15000</v>
-      </c>
-      <c r="AJ52" s="3">
-        <v>2100</v>
       </c>
       <c r="AK52" s="3">
         <v>2100</v>
       </c>
       <c r="AL52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AM52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E54" s="3">
         <v>29700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>31100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>29200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>29800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>28200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>28300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>30100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>30300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>32400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>32500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>31300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>31600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>30100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>35200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>35900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>38500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>41100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>40000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>39800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>40400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>49900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>50800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>51500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>52500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>50700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>56600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>55600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>24400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>23700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>23200</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,40 +5622,41 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E57" s="3">
         <v>4300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>4500</v>
       </c>
       <c r="J57" s="3">
         <v>4500</v>
       </c>
       <c r="K57" s="3">
-        <v>4200</v>
+        <v>4500</v>
       </c>
       <c r="L57" s="3">
         <v>4200</v>
       </c>
       <c r="M57" s="3">
-        <v>3300</v>
+        <v>4200</v>
       </c>
       <c r="N57" s="3">
         <v>3300</v>
@@ -5534,114 +5665,117 @@
         <v>3300</v>
       </c>
       <c r="P57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Q57" s="3">
         <v>4400</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>3500</v>
       </c>
       <c r="R57" s="3">
         <v>3500</v>
       </c>
       <c r="S57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="T57" s="3">
         <v>2600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>7200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>6800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>5400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>700</v>
+      </c>
+      <c r="E58" s="3">
         <v>1100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1000</v>
       </c>
       <c r="H58" s="3">
         <v>1000</v>
       </c>
       <c r="I58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J58" s="3">
         <v>800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>600</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -5659,40 +5793,40 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>800</v>
-      </c>
-      <c r="V58" s="3">
-        <v>200</v>
       </c>
       <c r="W58" s="3">
         <v>200</v>
       </c>
       <c r="X58" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y58" s="3">
         <v>1500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>900</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
       <c r="AB58" s="3">
         <v>0</v>
       </c>
       <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
         <v>2000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2600</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>900</v>
       </c>
       <c r="AG58" s="3">
         <v>900</v>
@@ -5703,8 +5837,8 @@
       <c r="AI58" s="3">
         <v>900</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>19</v>
+      <c r="AJ58" s="3">
+        <v>900</v>
       </c>
       <c r="AK58" s="3" t="s">
         <v>19</v>
@@ -5712,260 +5846,269 @@
       <c r="AL58" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="AM58" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E59" s="3">
         <v>6700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2300</v>
-      </c>
-      <c r="G59" s="3">
-        <v>3600</v>
       </c>
       <c r="H59" s="3">
         <v>3600</v>
       </c>
       <c r="I59" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J59" s="3">
         <v>2800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4400</v>
-      </c>
-      <c r="N59" s="3">
-        <v>4500</v>
       </c>
       <c r="O59" s="3">
         <v>4500</v>
       </c>
       <c r="P59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="Q59" s="3">
         <v>4900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3900</v>
-      </c>
-      <c r="T59" s="3">
-        <v>3800</v>
       </c>
       <c r="U59" s="3">
         <v>3800</v>
       </c>
       <c r="V59" s="3">
-        <v>4500</v>
+        <v>3800</v>
       </c>
       <c r="W59" s="3">
         <v>4500</v>
       </c>
       <c r="X59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="Y59" s="3">
         <v>5200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E60" s="3">
         <v>14900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>13400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11600</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>10600</v>
       </c>
       <c r="AB60" s="3">
         <v>10600</v>
       </c>
       <c r="AC60" s="3">
+        <v>10600</v>
+      </c>
+      <c r="AD60" s="3">
         <v>13200</v>
-      </c>
-      <c r="AD60" s="3">
-        <v>11300</v>
       </c>
       <c r="AE60" s="3">
         <v>11300</v>
       </c>
       <c r="AF60" s="3">
+        <v>11300</v>
+      </c>
+      <c r="AG60" s="3">
         <v>11000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>9400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1800</v>
-      </c>
-      <c r="G61" s="3">
-        <v>1700</v>
       </c>
       <c r="H61" s="3">
         <v>1700</v>
       </c>
       <c r="I61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J61" s="3">
         <v>700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>400</v>
-      </c>
-      <c r="K61" s="3">
-        <v>500</v>
       </c>
       <c r="L61" s="3">
         <v>500</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -5983,22 +6126,22 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="T61" s="3">
         <v>1900</v>
       </c>
       <c r="U61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="V61" s="3">
         <v>1000</v>
-      </c>
-      <c r="V61" s="3">
-        <v>1700</v>
       </c>
       <c r="W61" s="3">
         <v>1700</v>
       </c>
       <c r="X61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="Y61" s="3">
         <v>0</v>
@@ -6028,7 +6171,7 @@
         <v>0</v>
       </c>
       <c r="AH61" s="3">
-        <v>3100</v>
+        <v>0</v>
       </c>
       <c r="AI61" s="3">
         <v>3100</v>
@@ -6042,8 +6185,11 @@
       <c r="AL61" s="3">
         <v>3100</v>
       </c>
+      <c r="AM61" s="3">
+        <v>3100</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6051,109 +6197,112 @@
         <v>1200</v>
       </c>
       <c r="E62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F62" s="3">
         <v>1300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3200</v>
-      </c>
-      <c r="S62" s="3">
-        <v>3500</v>
       </c>
       <c r="T62" s="3">
         <v>3500</v>
       </c>
       <c r="U62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="V62" s="3">
         <v>3000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>5200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>8300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>10700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>10800</v>
-      </c>
-      <c r="AJ62" s="3">
-        <v>500</v>
       </c>
       <c r="AK62" s="3">
         <v>500</v>
       </c>
       <c r="AL62" s="3">
+        <v>500</v>
+      </c>
+      <c r="AM62" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E66" s="3">
         <v>20200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>21000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>14400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>16300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>22100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>18700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>18800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>17400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>23800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>22900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>9700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>9200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,109 +7243,112 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-49800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-48300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-47600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-46500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-45500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-44000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-42900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-41000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-40600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-39800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-38300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-36900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-36600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-35700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-35800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-35900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-37400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-37800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-39500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-35500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-35200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-34600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-33400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-32900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-32300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-32000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-28700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-24300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-23700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-22900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-22800</v>
-      </c>
-      <c r="AH72" s="3">
-        <v>-23100</v>
       </c>
       <c r="AI72" s="3">
         <v>-23100</v>
       </c>
       <c r="AJ72" s="3">
-        <v>-22800</v>
+        <v>-23100</v>
       </c>
       <c r="AK72" s="3">
         <v>-22800</v>
@@ -7182,8 +7356,11 @@
       <c r="AL72" s="3">
         <v>-22800</v>
       </c>
+      <c r="AM72" s="3">
+        <v>-22800</v>
+      </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E76" s="3">
         <v>9600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>21100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>21500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>22100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>23300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>23700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>24200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>24600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>27800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>32100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>32600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>33300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>33200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>32900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>32700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>14700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>14500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-900</v>
-      </c>
-      <c r="P81" s="3">
-        <v>100</v>
       </c>
       <c r="Q81" s="3">
         <v>100</v>
       </c>
       <c r="R81" s="3">
+        <v>100</v>
+      </c>
+      <c r="S81" s="3">
         <v>1500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-800</v>
       </c>
-      <c r="AF81" s="3">
-        <v>0</v>
-      </c>
       <c r="AG81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="3">
         <v>300</v>
       </c>
-      <c r="AH81" s="3">
-        <v>0</v>
-      </c>
       <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ81" s="3">
-        <v>0</v>
-      </c>
       <c r="AK81" s="3">
         <v>0</v>
       </c>
       <c r="AL81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,8 +8195,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8009,10 +8208,10 @@
         <v>100</v>
       </c>
       <c r="F83" s="3">
+        <v>100</v>
+      </c>
+      <c r="G83" s="3">
         <v>200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -8075,7 +8274,7 @@
         <v>100</v>
       </c>
       <c r="AB83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC83" s="3">
         <v>200</v>
@@ -8099,7 +8298,7 @@
         <v>200</v>
       </c>
       <c r="AJ83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AK83" s="3">
         <v>100</v>
@@ -8107,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>100</v>
       </c>
+      <c r="AM83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4200</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-200</v>
       </c>
       <c r="G89" s="3">
         <v>-200</v>
       </c>
       <c r="H89" s="3">
-        <v>200</v>
+        <v>-200</v>
       </c>
       <c r="I89" s="3">
         <v>200</v>
       </c>
       <c r="J89" s="3">
+        <v>200</v>
+      </c>
+      <c r="K89" s="3">
         <v>-1200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>300</v>
       </c>
       <c r="R89" s="3">
         <v>300</v>
       </c>
       <c r="S89" s="3">
+        <v>300</v>
+      </c>
+      <c r="T89" s="3">
         <v>-500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,8 +9027,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8819,31 +9040,31 @@
         <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>-100</v>
@@ -8852,14 +9073,14 @@
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -8873,11 +9094,11 @@
         <v>0</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
@@ -8888,22 +9109,22 @@
         <v>0</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>-100</v>
       </c>
       <c r="AI91" s="3">
         <v>-100</v>
@@ -8915,10 +9136,13 @@
         <v>-100</v>
       </c>
       <c r="AL91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,8 +9364,11 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9149,47 +9379,47 @@
         <v>-100</v>
       </c>
       <c r="F94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3" t="s">
+      <c r="M94" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
@@ -9197,13 +9427,13 @@
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y94" s="3">
         <v>-100</v>
@@ -9212,43 +9442,46 @@
         <v>-100</v>
       </c>
       <c r="AA94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>5000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>1300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>500</v>
-      </c>
-      <c r="AJ94" s="3">
-        <v>-100</v>
       </c>
       <c r="AK94" s="3">
         <v>-100</v>
       </c>
       <c r="AL94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM94" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9319,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,41 +9970,44 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>500</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
-      <c r="L100" s="3" t="s">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
@@ -9781,64 +10027,67 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>1900</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>900</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1700</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
       <c r="AI100" s="3">
         <v>0</v>
       </c>
       <c r="AJ100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AK100" s="3">
         <v>100</v>
       </c>
       <c r="AL100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM100" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9869,8 +10118,8 @@
       <c r="L101" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9947,114 +10196,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1000</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-2600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1900</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TGEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TGEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>TGEN</t>
   </si>
@@ -656,518 +656,530 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E8" s="3">
         <v>7200</v>
-      </c>
-      <c r="E8" s="3">
-        <v>7300</v>
       </c>
       <c r="F8" s="3">
         <v>7300</v>
       </c>
       <c r="G8" s="3">
+        <v>7300</v>
+      </c>
+      <c r="H8" s="3">
         <v>6100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5000</v>
-      </c>
-      <c r="U8" s="3">
-        <v>6100</v>
       </c>
       <c r="V8" s="3">
         <v>6100</v>
       </c>
       <c r="W8" s="3">
+        <v>6100</v>
+      </c>
+      <c r="X8" s="3">
         <v>5700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8000</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>8700</v>
       </c>
       <c r="AB8" s="3">
         <v>8700</v>
       </c>
       <c r="AC8" s="3">
+        <v>8700</v>
+      </c>
+      <c r="AD8" s="3">
         <v>7900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>10300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>8500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>6800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>7100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E9" s="3">
         <v>5000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2200</v>
-      </c>
-      <c r="P9" s="3">
-        <v>3700</v>
       </c>
       <c r="Q9" s="3">
         <v>3700</v>
       </c>
       <c r="R9" s="3">
+        <v>3700</v>
+      </c>
+      <c r="S9" s="3">
         <v>4300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>6300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>5200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>4400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,7 +1236,7 @@
         <v>300</v>
       </c>
       <c r="G12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H12" s="3">
         <v>200</v>
@@ -1232,10 +1245,10 @@
         <v>200</v>
       </c>
       <c r="J12" s="3">
+        <v>200</v>
+      </c>
+      <c r="K12" s="3">
         <v>300</v>
-      </c>
-      <c r="K12" s="3">
-        <v>200</v>
       </c>
       <c r="L12" s="3">
         <v>200</v>
@@ -1256,13 +1269,13 @@
         <v>200</v>
       </c>
       <c r="R12" s="3">
+        <v>200</v>
+      </c>
+      <c r="S12" s="3">
         <v>100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>200</v>
-      </c>
-      <c r="T12" s="3">
-        <v>100</v>
       </c>
       <c r="U12" s="3">
         <v>100</v>
@@ -1277,10 +1290,10 @@
         <v>100</v>
       </c>
       <c r="Y12" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z12" s="3">
         <v>200</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>400</v>
       </c>
       <c r="AA12" s="3">
         <v>400</v>
@@ -1292,7 +1305,7 @@
         <v>400</v>
       </c>
       <c r="AD12" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AE12" s="3">
         <v>300</v>
@@ -1301,16 +1314,16 @@
         <v>300</v>
       </c>
       <c r="AG12" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH12" s="3">
         <v>400</v>
-      </c>
-      <c r="AH12" s="3">
-        <v>300</v>
       </c>
       <c r="AI12" s="3">
         <v>300</v>
       </c>
       <c r="AJ12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AK12" s="3">
         <v>200</v>
@@ -1319,13 +1332,16 @@
         <v>200</v>
       </c>
       <c r="AM12" s="3">
+        <v>200</v>
+      </c>
+      <c r="AN12" s="3">
         <v>100</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1440,26 +1456,29 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
@@ -1470,17 +1489,17 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1494,43 +1513,43 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-2400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-1900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2900</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>19</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE14" s="3">
         <v>3700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>4400</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>19</v>
@@ -1547,8 +1566,8 @@
       <c r="AK14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
+      <c r="AL14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="AM14" s="3">
         <v>0</v>
@@ -1556,13 +1575,16 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
@@ -1571,7 +1593,7 @@
         <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -1586,17 +1608,17 @@
         <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>200</v>
       </c>
       <c r="N15" s="3">
+        <v>200</v>
+      </c>
+      <c r="O15" s="3">
         <v>100</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1672,8 +1694,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1736,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E17" s="3">
         <v>9300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7700</v>
-      </c>
-      <c r="L17" s="3">
-        <v>7500</v>
       </c>
       <c r="M17" s="3">
         <v>7500</v>
       </c>
       <c r="N17" s="3">
+        <v>7500</v>
+      </c>
+      <c r="O17" s="3">
         <v>6800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9100</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>9200</v>
       </c>
       <c r="AB17" s="3">
         <v>9200</v>
       </c>
       <c r="AC17" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AD17" s="3">
         <v>8200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>11500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>13700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>10100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>7800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>6800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>7100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-900</v>
       </c>
       <c r="H18" s="3">
         <v>-900</v>
       </c>
       <c r="I18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-800</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-1400</v>
       </c>
       <c r="O18" s="3">
         <v>-1400</v>
       </c>
       <c r="P18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-800</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
       <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
         <v>200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-4100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1100</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-500</v>
       </c>
       <c r="AB18" s="3">
         <v>-500</v>
       </c>
       <c r="AC18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>-600</v>
       </c>
       <c r="AG18" s="3">
         <v>-600</v>
       </c>
       <c r="AH18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AI18" s="3">
         <v>100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-200</v>
       </c>
-      <c r="AL18" s="3">
-        <v>0</v>
-      </c>
       <c r="AM18" s="3">
         <v>0</v>
       </c>
       <c r="AN18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1985,8 +2017,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1994,7 +2027,7 @@
         <v>-100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -2033,26 +2066,26 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
@@ -2069,20 +2102,20 @@
         <v>0</v>
       </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-100</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
         <v>0</v>
       </c>
@@ -2101,124 +2134,130 @@
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-400</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-800</v>
       </c>
       <c r="H21" s="3">
         <v>-800</v>
       </c>
       <c r="I21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J21" s="3">
         <v>-1300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-600</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-1300</v>
       </c>
       <c r="O21" s="3">
         <v>-1300</v>
       </c>
       <c r="P21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-700</v>
-      </c>
-      <c r="R21" s="3">
-        <v>200</v>
       </c>
       <c r="S21" s="3">
         <v>200</v>
       </c>
       <c r="T21" s="3">
+        <v>200</v>
+      </c>
+      <c r="U21" s="3">
         <v>1600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-4000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>-400</v>
       </c>
       <c r="AB21" s="3">
         <v>-400</v>
       </c>
       <c r="AC21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-100</v>
-      </c>
-      <c r="AL21" s="3">
-        <v>100</v>
       </c>
       <c r="AM21" s="3">
         <v>100</v>
       </c>
       <c r="AN21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AO21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2286,13 +2325,13 @@
         <v>0</v>
       </c>
       <c r="Y22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="3">
         <v>100</v>
       </c>
       <c r="AA22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -2304,11 +2343,11 @@
         <v>0</v>
       </c>
       <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
         <v>100</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
-      </c>
       <c r="AG22" s="3">
         <v>0</v>
       </c>
@@ -2333,124 +2372,130 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-800</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-1400</v>
       </c>
       <c r="O23" s="3">
         <v>-1400</v>
       </c>
       <c r="P23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-800</v>
-      </c>
-      <c r="R23" s="3">
-        <v>100</v>
       </c>
       <c r="S23" s="3">
         <v>100</v>
       </c>
       <c r="T23" s="3">
+        <v>100</v>
+      </c>
+      <c r="U23" s="3">
         <v>1500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-700</v>
       </c>
-      <c r="AH23" s="3">
-        <v>0</v>
-      </c>
       <c r="AI23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-300</v>
       </c>
-      <c r="AL23" s="3">
-        <v>0</v>
-      </c>
       <c r="AM23" s="3">
         <v>0</v>
       </c>
       <c r="AN23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -2466,24 +2511,24 @@
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -2544,14 +2589,14 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-      <c r="AH24" s="3" t="s">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AI24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ24" s="3" t="s">
-        <v>19</v>
+      <c r="AJ24" s="3">
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="s">
         <v>19</v>
@@ -2565,8 +2610,11 @@
       <c r="AN24" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="AO24" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2729,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-800</v>
-      </c>
-      <c r="R26" s="3">
-        <v>100</v>
       </c>
       <c r="S26" s="3">
         <v>100</v>
       </c>
       <c r="T26" s="3">
+        <v>100</v>
+      </c>
+      <c r="U26" s="3">
         <v>1500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-700</v>
       </c>
-      <c r="AH26" s="3">
-        <v>0</v>
-      </c>
       <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-300</v>
       </c>
-      <c r="AL26" s="3">
-        <v>0</v>
-      </c>
       <c r="AM26" s="3">
         <v>0</v>
       </c>
       <c r="AN26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-900</v>
-      </c>
-      <c r="R27" s="3">
-        <v>100</v>
       </c>
       <c r="S27" s="3">
         <v>100</v>
       </c>
       <c r="T27" s="3">
+        <v>100</v>
+      </c>
+      <c r="U27" s="3">
         <v>1500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-800</v>
       </c>
-      <c r="AH27" s="3">
-        <v>0</v>
-      </c>
       <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>300</v>
       </c>
-      <c r="AJ27" s="3">
-        <v>0</v>
-      </c>
       <c r="AK27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="3">
         <v>-300</v>
       </c>
-      <c r="AL27" s="3">
-        <v>0</v>
-      </c>
       <c r="AM27" s="3">
         <v>0</v>
       </c>
       <c r="AN27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3086,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,8 +3205,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,8 +3443,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3386,7 +3455,7 @@
         <v>100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -3425,26 +3494,26 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -3461,20 +3530,20 @@
         <v>0</v>
       </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>100</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
         <v>0</v>
       </c>
@@ -3493,124 +3562,130 @@
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-900</v>
-      </c>
-      <c r="R33" s="3">
-        <v>100</v>
       </c>
       <c r="S33" s="3">
         <v>100</v>
       </c>
       <c r="T33" s="3">
+        <v>100</v>
+      </c>
+      <c r="U33" s="3">
         <v>1500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-800</v>
       </c>
-      <c r="AH33" s="3">
-        <v>0</v>
-      </c>
       <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>300</v>
       </c>
-      <c r="AJ33" s="3">
-        <v>0</v>
-      </c>
       <c r="AK33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="3">
         <v>-300</v>
       </c>
-      <c r="AL33" s="3">
-        <v>0</v>
-      </c>
       <c r="AM33" s="3">
         <v>0</v>
       </c>
       <c r="AN33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3800,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-900</v>
-      </c>
-      <c r="R35" s="3">
-        <v>100</v>
       </c>
       <c r="S35" s="3">
         <v>100</v>
       </c>
       <c r="T35" s="3">
+        <v>100</v>
+      </c>
+      <c r="U35" s="3">
         <v>1500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-800</v>
       </c>
-      <c r="AH35" s="3">
-        <v>0</v>
-      </c>
       <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>300</v>
       </c>
-      <c r="AJ35" s="3">
-        <v>0</v>
-      </c>
       <c r="AK35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="3">
         <v>-300</v>
       </c>
-      <c r="AL35" s="3">
-        <v>0</v>
-      </c>
       <c r="AM35" s="3">
         <v>0</v>
       </c>
       <c r="AN35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,124 +4131,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E41" s="3">
         <v>15300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2900</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>900</v>
       </c>
       <c r="AA41" s="3">
         <v>900</v>
       </c>
       <c r="AB41" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC41" s="3">
         <v>800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>3700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4278,225 +4367,231 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E43" s="3">
         <v>6300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6400</v>
-      </c>
-      <c r="H43" s="3">
-        <v>6600</v>
       </c>
       <c r="I43" s="3">
         <v>6600</v>
       </c>
       <c r="J43" s="3">
+        <v>6600</v>
+      </c>
+      <c r="K43" s="3">
         <v>7800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>12200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>12900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>14300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>13000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>17100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>20000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>18100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>17500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>16900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>19100</v>
-      </c>
-      <c r="AF43" s="3">
-        <v>16000</v>
       </c>
       <c r="AG43" s="3">
         <v>16000</v>
       </c>
       <c r="AH43" s="3">
+        <v>16000</v>
+      </c>
+      <c r="AI43" s="3">
         <v>16500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>14100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>14700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>12500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>11800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>11200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E44" s="3">
         <v>9600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>9600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>9900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>10100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>10000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>10600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>11000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>12000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>11900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8200</v>
-      </c>
-      <c r="R44" s="3">
-        <v>7800</v>
       </c>
       <c r="S44" s="3">
         <v>7800</v>
       </c>
       <c r="T44" s="3">
+        <v>7800</v>
+      </c>
+      <c r="U44" s="3">
         <v>7900</v>
-      </c>
-      <c r="U44" s="3">
-        <v>6800</v>
       </c>
       <c r="V44" s="3">
         <v>6800</v>
       </c>
       <c r="W44" s="3">
+        <v>6800</v>
+      </c>
+      <c r="X44" s="3">
         <v>7200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>7100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>7300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>7500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>7100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>7000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>6700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>6300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>6000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5500</v>
-      </c>
-      <c r="AH44" s="3">
-        <v>5100</v>
       </c>
       <c r="AI44" s="3">
         <v>5100</v>
       </c>
       <c r="AJ44" s="3">
-        <v>6100</v>
+        <v>5100</v>
       </c>
       <c r="AK44" s="3">
         <v>6100</v>
@@ -4505,13 +4600,16 @@
         <v>6100</v>
       </c>
       <c r="AM44" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AN44" s="3">
         <v>4800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4548,14 +4646,14 @@
       <c r="N45" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>600</v>
       </c>
       <c r="R45" s="3">
         <v>600</v>
@@ -4567,19 +4665,19 @@
         <v>600</v>
       </c>
       <c r="U45" s="3">
+        <v>600</v>
+      </c>
+      <c r="V45" s="3">
         <v>800</v>
-      </c>
-      <c r="V45" s="3">
-        <v>600</v>
       </c>
       <c r="W45" s="3">
         <v>600</v>
       </c>
       <c r="X45" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y45" s="3">
         <v>500</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>600</v>
       </c>
       <c r="Z45" s="3">
         <v>600</v>
@@ -4597,182 +4695,188 @@
         <v>600</v>
       </c>
       <c r="AE45" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF45" s="3">
         <v>700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>800</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>900</v>
       </c>
       <c r="AH45" s="3">
         <v>900</v>
       </c>
       <c r="AI45" s="3">
+        <v>900</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E46" s="3">
         <v>32100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>20600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>20300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>22000</v>
-      </c>
-      <c r="P46" s="3">
-        <v>23400</v>
       </c>
       <c r="Q46" s="3">
         <v>23400</v>
       </c>
       <c r="R46" s="3">
+        <v>23400</v>
+      </c>
+      <c r="S46" s="3">
         <v>25600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>25000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>24700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>23200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>23300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>22200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>23600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>23800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>26100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>27900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>26600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>26200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>26800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>26400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>22900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>23400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>23700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>21700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>23600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>22700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>20600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>20100</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F47" s="3">
         <v>100</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>19</v>
+      <c r="G47" s="3">
+        <v>100</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I47" s="3">
-        <v>100</v>
+      <c r="I47" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="J47" s="3">
         <v>100</v>
       </c>
-      <c r="K47" s="3" t="s">
+      <c r="K47" s="3">
+        <v>100</v>
+      </c>
+      <c r="L47" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="L47" s="3">
-        <v>100</v>
       </c>
       <c r="M47" s="3">
         <v>100</v>
@@ -4789,8 +4893,8 @@
       <c r="Q47" s="3">
         <v>100</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>19</v>
+      <c r="R47" s="3">
+        <v>100</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>19</v>
@@ -4807,8 +4911,8 @@
       <c r="W47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -4849,124 +4953,127 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
-      <c r="AL47" s="3" t="s">
-        <v>19</v>
+      <c r="AL47" s="3">
+        <v>0</v>
       </c>
       <c r="AM47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AN47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO47" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E48" s="3">
         <v>4700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>11300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>11100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>11400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>15500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>15700</v>
-      </c>
-      <c r="AL48" s="3">
-        <v>500</v>
       </c>
       <c r="AM48" s="3">
         <v>500</v>
@@ -4974,49 +5081,52 @@
       <c r="AN48" s="3">
         <v>500</v>
       </c>
+      <c r="AO48" s="3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E49" s="3">
         <v>4600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5300</v>
-      </c>
-      <c r="J49" s="3">
-        <v>5200</v>
       </c>
       <c r="K49" s="3">
         <v>5200</v>
       </c>
       <c r="L49" s="3">
+        <v>5200</v>
+      </c>
+      <c r="M49" s="3">
         <v>5400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5600</v>
-      </c>
-      <c r="N49" s="3">
-        <v>3400</v>
       </c>
       <c r="O49" s="3">
         <v>3400</v>
       </c>
       <c r="P49" s="3">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="Q49" s="3">
         <v>3500</v>
@@ -5025,46 +5135,46 @@
         <v>3500</v>
       </c>
       <c r="S49" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="T49" s="3">
         <v>3600</v>
       </c>
       <c r="U49" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="V49" s="3">
         <v>3700</v>
       </c>
       <c r="W49" s="3">
+        <v>3700</v>
+      </c>
+      <c r="X49" s="3">
         <v>3800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6700</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>6900</v>
       </c>
       <c r="AB49" s="3">
         <v>6900</v>
       </c>
       <c r="AC49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="AD49" s="3">
         <v>6800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>6900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>11900</v>
-      </c>
-      <c r="AF49" s="3">
-        <v>16300</v>
       </c>
       <c r="AG49" s="3">
         <v>16300</v>
@@ -5076,13 +5186,13 @@
         <v>16300</v>
       </c>
       <c r="AJ49" s="3">
+        <v>16300</v>
+      </c>
+      <c r="AK49" s="3">
         <v>2500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2100</v>
-      </c>
-      <c r="AL49" s="3">
-        <v>1100</v>
       </c>
       <c r="AM49" s="3">
         <v>1100</v>
@@ -5090,8 +5200,11 @@
       <c r="AN49" s="3">
         <v>1100</v>
       </c>
+      <c r="AO49" s="3">
+        <v>1100</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,13 +5438,16 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E52" s="3">
         <v>100</v>
@@ -5337,22 +5456,22 @@
         <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>200</v>
       </c>
       <c r="I52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
       </c>
       <c r="K52" s="3">
+        <v>100</v>
+      </c>
+      <c r="L52" s="3">
         <v>200</v>
-      </c>
-      <c r="L52" s="3">
-        <v>100</v>
       </c>
       <c r="M52" s="3">
         <v>100</v>
@@ -5370,13 +5489,13 @@
         <v>100</v>
       </c>
       <c r="R52" s="3">
+        <v>100</v>
+      </c>
+      <c r="S52" s="3">
         <v>200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>100</v>
-      </c>
-      <c r="T52" s="3">
-        <v>200</v>
       </c>
       <c r="U52" s="3">
         <v>200</v>
@@ -5394,22 +5513,22 @@
         <v>200</v>
       </c>
       <c r="Z52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA52" s="3">
         <v>300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>700</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>600</v>
       </c>
       <c r="AC52" s="3">
         <v>600</v>
       </c>
       <c r="AD52" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE52" s="3">
         <v>300</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>400</v>
       </c>
       <c r="AF52" s="3">
         <v>400</v>
@@ -5418,28 +5537,31 @@
         <v>400</v>
       </c>
       <c r="AH52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AI52" s="3">
         <v>500</v>
       </c>
       <c r="AJ52" s="3">
+        <v>500</v>
+      </c>
+      <c r="AK52" s="3">
         <v>15100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>15000</v>
-      </c>
-      <c r="AL52" s="3">
-        <v>2100</v>
       </c>
       <c r="AM52" s="3">
         <v>2100</v>
       </c>
       <c r="AN52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AO52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E54" s="3">
         <v>41500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>28400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>29700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>31100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>28500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>29200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>28200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>28300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>30100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>30300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>32800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>32400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>32500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>31300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>31600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>30100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>35200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>35900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>38500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>41100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>40000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>39800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>40400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>49900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>50800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>51500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>52500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>50700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>56600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>55600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>24400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>23700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>23200</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,8 +5883,9 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5763,37 +5893,37 @@
         <v>3400</v>
       </c>
       <c r="E57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F57" s="3">
         <v>4900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>4500</v>
       </c>
       <c r="L57" s="3">
         <v>4500</v>
       </c>
       <c r="M57" s="3">
-        <v>4200</v>
+        <v>4500</v>
       </c>
       <c r="N57" s="3">
         <v>4200</v>
       </c>
       <c r="O57" s="3">
-        <v>3300</v>
+        <v>4200</v>
       </c>
       <c r="P57" s="3">
         <v>3300</v>
@@ -5802,76 +5932,79 @@
         <v>3300</v>
       </c>
       <c r="R57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="S57" s="3">
         <v>4400</v>
-      </c>
-      <c r="S57" s="3">
-        <v>3500</v>
       </c>
       <c r="T57" s="3">
         <v>3500</v>
       </c>
       <c r="U57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="V57" s="3">
         <v>2600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>6500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>6200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>7200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>6800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>5100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>5400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>4000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5879,43 +6012,43 @@
         <v>800</v>
       </c>
       <c r="E58" s="3">
+        <v>800</v>
+      </c>
+      <c r="F58" s="3">
         <v>700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1000</v>
       </c>
       <c r="J58" s="3">
         <v>1000</v>
       </c>
       <c r="K58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L58" s="3">
         <v>800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>600</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -5933,40 +6066,40 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>800</v>
-      </c>
-      <c r="X58" s="3">
-        <v>200</v>
       </c>
       <c r="Y58" s="3">
         <v>200</v>
       </c>
       <c r="Z58" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA58" s="3">
         <v>1500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>900</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
       <c r="AD58" s="3">
         <v>0</v>
       </c>
       <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3">
         <v>2000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2600</v>
-      </c>
-      <c r="AH58" s="3">
-        <v>900</v>
       </c>
       <c r="AI58" s="3">
         <v>900</v>
@@ -5977,8 +6110,8 @@
       <c r="AK58" s="3">
         <v>900</v>
       </c>
-      <c r="AL58" s="3" t="s">
-        <v>19</v>
+      <c r="AL58" s="3">
+        <v>900</v>
       </c>
       <c r="AM58" s="3" t="s">
         <v>19</v>
@@ -5986,278 +6119,287 @@
       <c r="AN58" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="AO58" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E59" s="3">
         <v>4600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>3600</v>
       </c>
       <c r="J59" s="3">
         <v>3600</v>
       </c>
       <c r="K59" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L59" s="3">
         <v>2800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4400</v>
-      </c>
-      <c r="P59" s="3">
-        <v>4500</v>
       </c>
       <c r="Q59" s="3">
         <v>4500</v>
       </c>
       <c r="R59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="S59" s="3">
         <v>4900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3900</v>
-      </c>
-      <c r="V59" s="3">
-        <v>3800</v>
       </c>
       <c r="W59" s="3">
         <v>3800</v>
       </c>
       <c r="X59" s="3">
-        <v>4500</v>
+        <v>3800</v>
       </c>
       <c r="Y59" s="3">
         <v>4500</v>
       </c>
       <c r="Z59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="AA59" s="3">
         <v>5200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E60" s="3">
         <v>11800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>12200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>13400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>11600</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>10600</v>
       </c>
       <c r="AD60" s="3">
         <v>10600</v>
       </c>
       <c r="AE60" s="3">
+        <v>10600</v>
+      </c>
+      <c r="AF60" s="3">
         <v>13200</v>
-      </c>
-      <c r="AF60" s="3">
-        <v>11300</v>
       </c>
       <c r="AG60" s="3">
         <v>11300</v>
       </c>
       <c r="AH60" s="3">
+        <v>11300</v>
+      </c>
+      <c r="AI60" s="3">
         <v>11000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>8700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>9400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>8500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>6100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>5600</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1800</v>
-      </c>
-      <c r="I61" s="3">
-        <v>1700</v>
       </c>
       <c r="J61" s="3">
         <v>1700</v>
       </c>
       <c r="K61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L61" s="3">
         <v>700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>400</v>
-      </c>
-      <c r="M61" s="3">
-        <v>500</v>
       </c>
       <c r="N61" s="3">
         <v>500</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -6275,22 +6417,22 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="V61" s="3">
         <v>1900</v>
       </c>
       <c r="W61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="X61" s="3">
         <v>1000</v>
-      </c>
-      <c r="X61" s="3">
-        <v>1700</v>
       </c>
       <c r="Y61" s="3">
         <v>1700</v>
       </c>
       <c r="Z61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="AA61" s="3">
         <v>0</v>
@@ -6320,7 +6462,7 @@
         <v>0</v>
       </c>
       <c r="AJ61" s="3">
-        <v>3100</v>
+        <v>0</v>
       </c>
       <c r="AK61" s="3">
         <v>3100</v>
@@ -6334,124 +6476,130 @@
       <c r="AN61" s="3">
         <v>3100</v>
       </c>
+      <c r="AO61" s="3">
+        <v>3100</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1200</v>
       </c>
       <c r="F62" s="3">
         <v>1200</v>
       </c>
       <c r="G62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H62" s="3">
         <v>1300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3200</v>
-      </c>
-      <c r="U62" s="3">
-        <v>3500</v>
       </c>
       <c r="V62" s="3">
         <v>3500</v>
       </c>
       <c r="W62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="X62" s="3">
         <v>3000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>8700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>7800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>8300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>10700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>10800</v>
-      </c>
-      <c r="AL62" s="3">
-        <v>500</v>
       </c>
       <c r="AM62" s="3">
         <v>500</v>
       </c>
       <c r="AN62" s="3">
+        <v>500</v>
+      </c>
+      <c r="AO62" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6952,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E66" s="3">
         <v>16100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>19400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>21000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>17800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>15900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>22100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>18700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>18800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>19200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>17400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>23800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>22900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>9700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>9200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7352,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7471,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,115 +7590,118 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-55900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-51900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-49800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-48300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-47600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-46500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-45500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-44000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-42900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-41000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-40600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-39800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-38300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-36900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-36600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-35700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-35800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-35900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-37400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-37800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-39500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-35500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-35200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-34600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-33400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-32900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-32300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-32000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-28700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-24300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-23700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-22900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-22800</v>
-      </c>
-      <c r="AJ72" s="3">
-        <v>-23100</v>
       </c>
       <c r="AK72" s="3">
         <v>-23100</v>
       </c>
       <c r="AL72" s="3">
-        <v>-22800</v>
+        <v>-23100</v>
       </c>
       <c r="AM72" s="3">
         <v>-22800</v>
@@ -7536,8 +7709,11 @@
       <c r="AN72" s="3">
         <v>-22800</v>
       </c>
+      <c r="AO72" s="3">
+        <v>-22800</v>
+      </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E76" s="3">
         <v>25500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>21400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>21200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>21100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>19100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>21300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>21500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>22100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>23300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>23700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>24200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>24600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>27800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>32100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>32600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>33300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>33200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>32900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>32700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>14700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>14500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8304,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-900</v>
-      </c>
-      <c r="R81" s="3">
-        <v>100</v>
       </c>
       <c r="S81" s="3">
         <v>100</v>
       </c>
       <c r="T81" s="3">
+        <v>100</v>
+      </c>
+      <c r="U81" s="3">
         <v>1500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-800</v>
       </c>
-      <c r="AH81" s="3">
-        <v>0</v>
-      </c>
       <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>300</v>
       </c>
-      <c r="AJ81" s="3">
-        <v>0</v>
-      </c>
       <c r="AK81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL81" s="3">
         <v>-300</v>
       </c>
-      <c r="AL81" s="3">
-        <v>0</v>
-      </c>
       <c r="AM81" s="3">
         <v>0</v>
       </c>
       <c r="AN81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,8 +8592,9 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8413,10 +8611,10 @@
         <v>100</v>
       </c>
       <c r="H83" s="3">
+        <v>100</v>
+      </c>
+      <c r="I83" s="3">
         <v>200</v>
-      </c>
-      <c r="I83" s="3">
-        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
@@ -8479,7 +8677,7 @@
         <v>100</v>
       </c>
       <c r="AD83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AE83" s="3">
         <v>200</v>
@@ -8503,7 +8701,7 @@
         <v>200</v>
       </c>
       <c r="AL83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AM83" s="3">
         <v>100</v>
@@ -8511,8 +8709,11 @@
       <c r="AN83" s="3">
         <v>100</v>
       </c>
+      <c r="AO83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9304,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4200</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-200</v>
       </c>
       <c r="I89" s="3">
         <v>-200</v>
       </c>
       <c r="J89" s="3">
-        <v>200</v>
+        <v>-200</v>
       </c>
       <c r="K89" s="3">
         <v>200</v>
       </c>
       <c r="L89" s="3">
+        <v>200</v>
+      </c>
+      <c r="M89" s="3">
         <v>-1200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1900</v>
-      </c>
-      <c r="S89" s="3">
-        <v>300</v>
       </c>
       <c r="T89" s="3">
         <v>300</v>
       </c>
       <c r="U89" s="3">
+        <v>300</v>
+      </c>
+      <c r="V89" s="3">
         <v>-500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,13 +9468,14 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
@@ -9267,31 +9487,31 @@
         <v>-100</v>
       </c>
       <c r="H91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>-100</v>
@@ -9300,14 +9520,14 @@
         <v>-100</v>
       </c>
       <c r="S91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
@@ -9321,11 +9541,11 @@
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
@@ -9336,22 +9556,22 @@
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
       <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AJ91" s="3">
-        <v>-100</v>
       </c>
       <c r="AK91" s="3">
         <v>-100</v>
@@ -9363,10 +9583,13 @@
         <v>-100</v>
       </c>
       <c r="AN91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AO91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,13 +9823,16 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E94" s="3">
         <v>-100</v>
@@ -9615,47 +9844,47 @@
         <v>-100</v>
       </c>
       <c r="H94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
@@ -9663,13 +9892,13 @@
         <v>0</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA94" s="3">
         <v>-100</v>
@@ -9678,43 +9907,46 @@
         <v>-100</v>
       </c>
       <c r="AC94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>5000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>500</v>
-      </c>
-      <c r="AL94" s="3">
-        <v>-100</v>
       </c>
       <c r="AM94" s="3">
         <v>-100</v>
       </c>
       <c r="AN94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AO94" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +9987,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9793,8 +10026,8 @@
       <c r="N96" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9871,8 +10104,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,47 +10461,50 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>17200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
@@ -10279,64 +10524,67 @@
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>1900</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>900</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1700</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AJ100" s="3">
-        <v>0</v>
-      </c>
       <c r="AK100" s="3">
         <v>0</v>
       </c>
       <c r="AL100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AM100" s="3">
         <v>100</v>
       </c>
       <c r="AN100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AO100" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10373,8 +10621,8 @@
       <c r="N101" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10451,120 +10699,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E102" s="3">
         <v>13600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1000</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-2600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1900</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-600</v>
       </c>
     </row>
